--- a/FMS2025.xlsx
+++ b/FMS2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\MY FILES\Onedrive\CV\dm-dut.github.io\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E1B83A-D570-498B-8F40-B6C97F4093A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB01A72F-6BC2-4F7A-852B-04E9B128C26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7027" uniqueCount="2412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7308" uniqueCount="2596">
   <si>
     <t>序号</t>
   </si>
@@ -7244,9 +7244,6 @@
   </si>
   <si>
     <t>Learning Organization</t>
-  </si>
-  <si>
-    <t>《FMS Journal Rating Guide 2025》由中国优选法统筹法与经济数学研究会、管理科学与工程学会、中国系统工程学会于2025年7月7日联合发布.</t>
   </si>
   <si>
     <t>FMS等级2025</t>
@@ -7259,6 +7256,561 @@
   <si>
     <t>FMS等级2020</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002-5502</t>
+  </si>
+  <si>
+    <t>管理世界</t>
+  </si>
+  <si>
+    <t>T1</t>
+  </si>
+  <si>
+    <t>0577-9154</t>
+  </si>
+  <si>
+    <t>经济研究</t>
+  </si>
+  <si>
+    <t>1007-9807</t>
+  </si>
+  <si>
+    <t>管理科学学报</t>
+  </si>
+  <si>
+    <t>1002-4921</t>
+  </si>
+  <si>
+    <t>中国社会科学</t>
+  </si>
+  <si>
+    <t>1008-3448</t>
+  </si>
+  <si>
+    <t>南开管理评论</t>
+  </si>
+  <si>
+    <t>1000-6788</t>
+  </si>
+  <si>
+    <t>系统工程理论与实践</t>
+  </si>
+  <si>
+    <t>1006-480X</t>
+  </si>
+  <si>
+    <t>中国工业经济</t>
+  </si>
+  <si>
+    <t>1002-7246</t>
+  </si>
+  <si>
+    <t>金融研究</t>
+  </si>
+  <si>
+    <t>1003-207X</t>
+  </si>
+  <si>
+    <t>中国管理科学</t>
+  </si>
+  <si>
+    <t>1003-2886</t>
+  </si>
+  <si>
+    <t>会计研究</t>
+  </si>
+  <si>
+    <t>2095-1086</t>
+  </si>
+  <si>
+    <t>经济学（季刊）</t>
+  </si>
+  <si>
+    <t>1002-9621</t>
+  </si>
+  <si>
+    <t>世界经济</t>
+  </si>
+  <si>
+    <t>1004-6062</t>
+  </si>
+  <si>
+    <t>管理工程学报</t>
+  </si>
+  <si>
+    <t>1672-6162</t>
+  </si>
+  <si>
+    <t>公共管理学报</t>
+  </si>
+  <si>
+    <t>1005-0566</t>
+  </si>
+  <si>
+    <t>中国软科学</t>
+  </si>
+  <si>
+    <t>1672-0334</t>
+  </si>
+  <si>
+    <t>管理科学</t>
+  </si>
+  <si>
+    <t>1000-3894</t>
+  </si>
+  <si>
+    <t>数量经济技术经济研究</t>
+  </si>
+  <si>
+    <t>0439-755X</t>
+  </si>
+  <si>
+    <t>心理学报</t>
+  </si>
+  <si>
+    <t>1000-2995</t>
+  </si>
+  <si>
+    <t>科研管理</t>
+  </si>
+  <si>
+    <t>1003-1952</t>
+  </si>
+  <si>
+    <t>管理评论</t>
+  </si>
+  <si>
+    <t>1003-2053</t>
+  </si>
+  <si>
+    <t>科学学研究</t>
+  </si>
+  <si>
+    <t>1000-0135</t>
+  </si>
+  <si>
+    <t>情报学报</t>
+  </si>
+  <si>
+    <t>1002-4565</t>
+  </si>
+  <si>
+    <t>统计研究</t>
+  </si>
+  <si>
+    <t>1002-8870</t>
+  </si>
+  <si>
+    <t>中国农村经济</t>
+  </si>
+  <si>
+    <t>1001-8867</t>
+  </si>
+  <si>
+    <t>中国图书馆学报</t>
+  </si>
+  <si>
+    <t>2097-0145</t>
+  </si>
+  <si>
+    <t>工程管理科技前沿</t>
+  </si>
+  <si>
+    <t>1672-884X</t>
+  </si>
+  <si>
+    <t>管理学报</t>
+  </si>
+  <si>
+    <t>2096-9732</t>
+  </si>
+  <si>
+    <t>计量经济学报</t>
+  </si>
+  <si>
+    <t>1000-5781</t>
+  </si>
+  <si>
+    <t>系统工程学报</t>
+  </si>
+  <si>
+    <t>T2</t>
+  </si>
+  <si>
+    <t>1006-0863</t>
+  </si>
+  <si>
+    <t>中国行政管理</t>
+  </si>
+  <si>
+    <t>1002-4239</t>
+  </si>
+  <si>
+    <t>审计研究</t>
+  </si>
+  <si>
+    <t>1002-8102</t>
+  </si>
+  <si>
+    <t>财贸经济</t>
+  </si>
+  <si>
+    <t>1005-2542</t>
+  </si>
+  <si>
+    <t>系统管理学报</t>
+  </si>
+  <si>
+    <t>1002-8390</t>
+  </si>
+  <si>
+    <t>经济学动态</t>
+  </si>
+  <si>
+    <t>1007-3221</t>
+  </si>
+  <si>
+    <t>1000-6389</t>
+  </si>
+  <si>
+    <t>农业经济问题</t>
+  </si>
+  <si>
+    <t>1002-0241</t>
+  </si>
+  <si>
+    <t>科学学与科学技术管理</t>
+  </si>
+  <si>
+    <t>1002-5839</t>
+  </si>
+  <si>
+    <t>经济科学</t>
+  </si>
+  <si>
+    <t>1001-9952</t>
+  </si>
+  <si>
+    <t>财经研究</t>
+  </si>
+  <si>
+    <t>1002-5766</t>
+  </si>
+  <si>
+    <t>经济管理</t>
+  </si>
+  <si>
+    <t>1002-2104</t>
+  </si>
+  <si>
+    <t>中国人口·资源与环境</t>
+  </si>
+  <si>
+    <t>1001-4691</t>
+  </si>
+  <si>
+    <t>南开经济研究</t>
+  </si>
+  <si>
+    <t>1004-8308</t>
+  </si>
+  <si>
+    <t>研究与发展管理</t>
+  </si>
+  <si>
+    <t>1006-1029</t>
+  </si>
+  <si>
+    <t>国际金融研究</t>
+  </si>
+  <si>
+    <t>1000-596X</t>
+  </si>
+  <si>
+    <t>经济理论与经济管理</t>
+  </si>
+  <si>
+    <t>1002-4670</t>
+  </si>
+  <si>
+    <t>国际贸易问题</t>
+  </si>
+  <si>
+    <t>1003-5656</t>
+  </si>
+  <si>
+    <t>经济学家</t>
+  </si>
+  <si>
+    <t>1003-2878</t>
+  </si>
+  <si>
+    <t>财政研究</t>
+  </si>
+  <si>
+    <t>2097-0099</t>
+  </si>
+  <si>
+    <t>营销科学学报</t>
+  </si>
+  <si>
+    <t>1007-5429</t>
+  </si>
+  <si>
+    <t>工业工程与管理</t>
+  </si>
+  <si>
+    <t>1002-1566</t>
+  </si>
+  <si>
+    <t>数理统计与管理</t>
+  </si>
+  <si>
+    <t>1003-7543</t>
+  </si>
+  <si>
+    <t>改革</t>
+  </si>
+  <si>
+    <t>1001-4950</t>
+  </si>
+  <si>
+    <t>外国经济与管理</t>
+  </si>
+  <si>
+    <t>1004-3306</t>
+  </si>
+  <si>
+    <t>保险研究</t>
+  </si>
+  <si>
+    <t>1006-4583</t>
+  </si>
+  <si>
+    <t>中国农村观察</t>
+  </si>
+  <si>
+    <t>1002-5006</t>
+  </si>
+  <si>
+    <t>旅游学刊</t>
+  </si>
+  <si>
+    <t>1003-3947</t>
+  </si>
+  <si>
+    <t>经济社会体制比较</t>
+  </si>
+  <si>
+    <t>1005-3425</t>
+  </si>
+  <si>
+    <t>经济评论</t>
+  </si>
+  <si>
+    <t>1000-0577</t>
+  </si>
+  <si>
+    <t>系统科学与数学</t>
+  </si>
+  <si>
+    <t>1007-6964</t>
+  </si>
+  <si>
+    <t>世界经济研究</t>
+  </si>
+  <si>
+    <t>1000-8462</t>
+  </si>
+  <si>
+    <t>经济地理</t>
+  </si>
+  <si>
+    <t>1007-0974</t>
+  </si>
+  <si>
+    <t>国际经济评论</t>
+  </si>
+  <si>
+    <t>1671-9301</t>
+  </si>
+  <si>
+    <t>产业经济研究</t>
+  </si>
+  <si>
+    <t>0253-9772</t>
+  </si>
+  <si>
+    <t>世界经济文汇</t>
+  </si>
+  <si>
+    <t>1000-6370</t>
+  </si>
+  <si>
+    <t>农业技术经济</t>
+  </si>
+  <si>
+    <t>1674-2486</t>
+  </si>
+  <si>
+    <t>公共行政评论</t>
+  </si>
+  <si>
+    <t>1000-7636</t>
+  </si>
+  <si>
+    <t>经济与管理研究</t>
+  </si>
+  <si>
+    <t>1008-2069</t>
+  </si>
+  <si>
+    <t>宏观经济研究</t>
+  </si>
+  <si>
+    <t>1000-8306</t>
+  </si>
+  <si>
+    <t>财经科学</t>
+  </si>
+  <si>
+    <t>1002-2848</t>
+  </si>
+  <si>
+    <t>当代经济科学</t>
+  </si>
+  <si>
+    <t>0252-3116</t>
+  </si>
+  <si>
+    <t>图书情报工作</t>
+  </si>
+  <si>
+    <t>1007-7588</t>
+  </si>
+  <si>
+    <t>资源科学</t>
+  </si>
+  <si>
+    <t>1005-0892</t>
+  </si>
+  <si>
+    <t>当代财经</t>
+  </si>
+  <si>
+    <t>1001-6260</t>
+  </si>
+  <si>
+    <t>财贸研究</t>
+  </si>
+  <si>
+    <t>1000-4181</t>
+  </si>
+  <si>
+    <t>中国经济问题</t>
+  </si>
+  <si>
+    <t>1004-4833</t>
+  </si>
+  <si>
+    <t>审计与经济研究</t>
+  </si>
+  <si>
+    <t>1003-2797</t>
+  </si>
+  <si>
+    <t>图书情报知识</t>
+  </si>
+  <si>
+    <t>1674-7690</t>
+  </si>
+  <si>
+    <t>金融评论</t>
+  </si>
+  <si>
+    <t>1009-6744</t>
+  </si>
+  <si>
+    <t>交通运输系统工程与信息</t>
+  </si>
+  <si>
+    <t>1009-9190</t>
+  </si>
+  <si>
+    <t>现代金融研究</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2096-3467</t>
+  </si>
+  <si>
+    <t>数据分析与知识发现</t>
+  </si>
+  <si>
+    <t>1000-6249</t>
+  </si>
+  <si>
+    <t>南方经济</t>
+  </si>
+  <si>
+    <t>1002-0594</t>
+  </si>
+  <si>
+    <t>国际经贸探索</t>
+  </si>
+  <si>
+    <t>1674-1625</t>
+  </si>
+  <si>
+    <t>金融经济学研究</t>
+  </si>
+  <si>
+    <t>2095-2171</t>
+  </si>
+  <si>
+    <t>信息资源管理学报</t>
+  </si>
+  <si>
+    <t>2096-9554</t>
+  </si>
+  <si>
+    <t>会计与经济研究</t>
+  </si>
+  <si>
+    <t>2096-7713</t>
+  </si>
+  <si>
+    <t>公共管理评论</t>
+  </si>
+  <si>
+    <t>2095-7254</t>
+  </si>
+  <si>
+    <t>经济学报</t>
+  </si>
+  <si>
+    <t>1672-7223</t>
+  </si>
+  <si>
+    <t>电子政务</t>
+  </si>
+  <si>
+    <t>——</t>
+  </si>
+  <si>
+    <t>管理学研究</t>
+  </si>
+  <si>
+    <t>信息系统学报</t>
+  </si>
+  <si>
+    <t>金融学季刊</t>
+  </si>
+  <si>
+    <t>珞珈管理评论</t>
+  </si>
+  <si>
+    <t>数量经济研究</t>
   </si>
 </sst>
 </file>
@@ -7608,7 +8160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I1185"/>
+  <dimension ref="A1:I1278"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="5" max="5" width="35.44140625" customWidth="1"/>
@@ -7628,13 +8180,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>2408</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>2409</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>2410</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>2411</v>
       </c>
       <c r="H1" t="s">
         <v>4</v>
@@ -41341,9 +41893,1320 @@
         <v>2.7</v>
       </c>
     </row>
-    <row r="1185" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1185" t="s">
-        <v>2408</v>
+    <row r="1185" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1185">
+        <v>1184</v>
+      </c>
+      <c r="C1185" t="s">
+        <v>2411</v>
+      </c>
+      <c r="D1185" t="s">
+        <v>2412</v>
+      </c>
+      <c r="E1185" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1186">
+        <v>1185</v>
+      </c>
+      <c r="C1186" t="s">
+        <v>2414</v>
+      </c>
+      <c r="D1186" t="s">
+        <v>2415</v>
+      </c>
+      <c r="E1186" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1187">
+        <v>1186</v>
+      </c>
+      <c r="C1187" t="s">
+        <v>2416</v>
+      </c>
+      <c r="D1187" t="s">
+        <v>2417</v>
+      </c>
+      <c r="E1187" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1188">
+        <v>1187</v>
+      </c>
+      <c r="C1188" t="s">
+        <v>2418</v>
+      </c>
+      <c r="D1188" t="s">
+        <v>2419</v>
+      </c>
+      <c r="E1188" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1189">
+        <v>1188</v>
+      </c>
+      <c r="C1189" t="s">
+        <v>2420</v>
+      </c>
+      <c r="D1189" t="s">
+        <v>2421</v>
+      </c>
+      <c r="E1189" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1190">
+        <v>1189</v>
+      </c>
+      <c r="C1190" t="s">
+        <v>2422</v>
+      </c>
+      <c r="D1190" t="s">
+        <v>2423</v>
+      </c>
+      <c r="E1190" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1191">
+        <v>1190</v>
+      </c>
+      <c r="C1191" t="s">
+        <v>2424</v>
+      </c>
+      <c r="D1191" t="s">
+        <v>2425</v>
+      </c>
+      <c r="E1191" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1192">
+        <v>1191</v>
+      </c>
+      <c r="C1192" t="s">
+        <v>2426</v>
+      </c>
+      <c r="D1192" t="s">
+        <v>2427</v>
+      </c>
+      <c r="E1192" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1193">
+        <v>1192</v>
+      </c>
+      <c r="C1193" t="s">
+        <v>2428</v>
+      </c>
+      <c r="D1193" t="s">
+        <v>2429</v>
+      </c>
+      <c r="E1193" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1194">
+        <v>1193</v>
+      </c>
+      <c r="C1194" t="s">
+        <v>2430</v>
+      </c>
+      <c r="D1194" t="s">
+        <v>2431</v>
+      </c>
+      <c r="E1194" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1195">
+        <v>1194</v>
+      </c>
+      <c r="C1195" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D1195" t="s">
+        <v>2433</v>
+      </c>
+      <c r="E1195" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1196">
+        <v>1195</v>
+      </c>
+      <c r="C1196" t="s">
+        <v>2434</v>
+      </c>
+      <c r="D1196" t="s">
+        <v>2435</v>
+      </c>
+      <c r="E1196" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1197">
+        <v>1196</v>
+      </c>
+      <c r="C1197" t="s">
+        <v>2436</v>
+      </c>
+      <c r="D1197" t="s">
+        <v>2437</v>
+      </c>
+      <c r="E1197" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1198">
+        <v>1197</v>
+      </c>
+      <c r="C1198" t="s">
+        <v>2438</v>
+      </c>
+      <c r="D1198" t="s">
+        <v>2439</v>
+      </c>
+      <c r="E1198" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1199">
+        <v>1198</v>
+      </c>
+      <c r="C1199" t="s">
+        <v>2440</v>
+      </c>
+      <c r="D1199" t="s">
+        <v>2441</v>
+      </c>
+      <c r="E1199" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1200">
+        <v>1199</v>
+      </c>
+      <c r="C1200" t="s">
+        <v>2442</v>
+      </c>
+      <c r="D1200" t="s">
+        <v>2443</v>
+      </c>
+      <c r="E1200" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1201">
+        <v>1200</v>
+      </c>
+      <c r="C1201" t="s">
+        <v>2444</v>
+      </c>
+      <c r="D1201" t="s">
+        <v>2445</v>
+      </c>
+      <c r="E1201" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1202">
+        <v>1201</v>
+      </c>
+      <c r="C1202" t="s">
+        <v>2446</v>
+      </c>
+      <c r="D1202" t="s">
+        <v>2447</v>
+      </c>
+      <c r="E1202" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1203">
+        <v>1202</v>
+      </c>
+      <c r="C1203" t="s">
+        <v>2448</v>
+      </c>
+      <c r="D1203" t="s">
+        <v>2449</v>
+      </c>
+      <c r="E1203" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1204">
+        <v>1203</v>
+      </c>
+      <c r="C1204" t="s">
+        <v>2450</v>
+      </c>
+      <c r="D1204" t="s">
+        <v>2451</v>
+      </c>
+      <c r="E1204" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1205">
+        <v>1204</v>
+      </c>
+      <c r="C1205" t="s">
+        <v>2452</v>
+      </c>
+      <c r="D1205" t="s">
+        <v>2453</v>
+      </c>
+      <c r="E1205" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1206">
+        <v>1205</v>
+      </c>
+      <c r="C1206" t="s">
+        <v>2454</v>
+      </c>
+      <c r="D1206" t="s">
+        <v>2455</v>
+      </c>
+      <c r="E1206" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1207">
+        <v>1206</v>
+      </c>
+      <c r="C1207" t="s">
+        <v>2456</v>
+      </c>
+      <c r="D1207" t="s">
+        <v>2457</v>
+      </c>
+      <c r="E1207" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1208">
+        <v>1207</v>
+      </c>
+      <c r="C1208" t="s">
+        <v>2458</v>
+      </c>
+      <c r="D1208" t="s">
+        <v>2459</v>
+      </c>
+      <c r="E1208" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1209">
+        <v>1208</v>
+      </c>
+      <c r="C1209" t="s">
+        <v>2460</v>
+      </c>
+      <c r="D1209" t="s">
+        <v>2461</v>
+      </c>
+      <c r="E1209" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1210">
+        <v>1209</v>
+      </c>
+      <c r="C1210" t="s">
+        <v>2462</v>
+      </c>
+      <c r="D1210" t="s">
+        <v>2463</v>
+      </c>
+      <c r="E1210" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1211">
+        <v>1210</v>
+      </c>
+      <c r="C1211" t="s">
+        <v>2464</v>
+      </c>
+      <c r="D1211" t="s">
+        <v>2465</v>
+      </c>
+      <c r="E1211" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1212">
+        <v>1211</v>
+      </c>
+      <c r="C1212" t="s">
+        <v>2466</v>
+      </c>
+      <c r="D1212" t="s">
+        <v>2467</v>
+      </c>
+      <c r="E1212" t="s">
+        <v>2413</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1213">
+        <v>1212</v>
+      </c>
+      <c r="C1213" t="s">
+        <v>2468</v>
+      </c>
+      <c r="D1213" t="s">
+        <v>2469</v>
+      </c>
+      <c r="E1213" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1214">
+        <v>1213</v>
+      </c>
+      <c r="C1214" t="s">
+        <v>2471</v>
+      </c>
+      <c r="D1214" t="s">
+        <v>2472</v>
+      </c>
+      <c r="E1214" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1215">
+        <v>1214</v>
+      </c>
+      <c r="C1215" t="s">
+        <v>2473</v>
+      </c>
+      <c r="D1215" t="s">
+        <v>2474</v>
+      </c>
+      <c r="E1215" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1216">
+        <v>1215</v>
+      </c>
+      <c r="C1216" t="s">
+        <v>2475</v>
+      </c>
+      <c r="D1216" t="s">
+        <v>2476</v>
+      </c>
+      <c r="E1216" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1217">
+        <v>1216</v>
+      </c>
+      <c r="C1217" t="s">
+        <v>2477</v>
+      </c>
+      <c r="D1217" t="s">
+        <v>2478</v>
+      </c>
+      <c r="E1217" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1218">
+        <v>1217</v>
+      </c>
+      <c r="C1218" t="s">
+        <v>2479</v>
+      </c>
+      <c r="D1218" t="s">
+        <v>2480</v>
+      </c>
+      <c r="E1218" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1219">
+        <v>1218</v>
+      </c>
+      <c r="C1219" t="s">
+        <v>2481</v>
+      </c>
+      <c r="D1219" t="s">
+        <v>2085</v>
+      </c>
+      <c r="E1219" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1220">
+        <v>1219</v>
+      </c>
+      <c r="C1220" t="s">
+        <v>2482</v>
+      </c>
+      <c r="D1220" t="s">
+        <v>2483</v>
+      </c>
+      <c r="E1220" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1221">
+        <v>1220</v>
+      </c>
+      <c r="C1221" t="s">
+        <v>2484</v>
+      </c>
+      <c r="D1221" t="s">
+        <v>2485</v>
+      </c>
+      <c r="E1221" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1222">
+        <v>1221</v>
+      </c>
+      <c r="C1222" t="s">
+        <v>2486</v>
+      </c>
+      <c r="D1222" t="s">
+        <v>2487</v>
+      </c>
+      <c r="E1222" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1223">
+        <v>1222</v>
+      </c>
+      <c r="C1223" t="s">
+        <v>2488</v>
+      </c>
+      <c r="D1223" t="s">
+        <v>2489</v>
+      </c>
+      <c r="E1223" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1224">
+        <v>1223</v>
+      </c>
+      <c r="C1224" t="s">
+        <v>2490</v>
+      </c>
+      <c r="D1224" t="s">
+        <v>2491</v>
+      </c>
+      <c r="E1224" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1225">
+        <v>1224</v>
+      </c>
+      <c r="C1225" t="s">
+        <v>2492</v>
+      </c>
+      <c r="D1225" t="s">
+        <v>2493</v>
+      </c>
+      <c r="E1225" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1226">
+        <v>1225</v>
+      </c>
+      <c r="C1226" t="s">
+        <v>2494</v>
+      </c>
+      <c r="D1226" t="s">
+        <v>2495</v>
+      </c>
+      <c r="E1226" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1227">
+        <v>1226</v>
+      </c>
+      <c r="C1227" t="s">
+        <v>2496</v>
+      </c>
+      <c r="D1227" t="s">
+        <v>2497</v>
+      </c>
+      <c r="E1227" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1228">
+        <v>1227</v>
+      </c>
+      <c r="C1228" t="s">
+        <v>2498</v>
+      </c>
+      <c r="D1228" t="s">
+        <v>2499</v>
+      </c>
+      <c r="E1228" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1229">
+        <v>1228</v>
+      </c>
+      <c r="C1229" t="s">
+        <v>2500</v>
+      </c>
+      <c r="D1229" t="s">
+        <v>2501</v>
+      </c>
+      <c r="E1229" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1230">
+        <v>1229</v>
+      </c>
+      <c r="C1230" t="s">
+        <v>2502</v>
+      </c>
+      <c r="D1230" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E1230" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1231">
+        <v>1230</v>
+      </c>
+      <c r="C1231" t="s">
+        <v>2504</v>
+      </c>
+      <c r="D1231" t="s">
+        <v>2505</v>
+      </c>
+      <c r="E1231" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1232">
+        <v>1231</v>
+      </c>
+      <c r="C1232" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D1232" t="s">
+        <v>2507</v>
+      </c>
+      <c r="E1232" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1233">
+        <v>1232</v>
+      </c>
+      <c r="C1233" t="s">
+        <v>2508</v>
+      </c>
+      <c r="D1233" t="s">
+        <v>2509</v>
+      </c>
+      <c r="E1233" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1234">
+        <v>1233</v>
+      </c>
+      <c r="C1234" t="s">
+        <v>2510</v>
+      </c>
+      <c r="D1234" t="s">
+        <v>2511</v>
+      </c>
+      <c r="E1234" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1235">
+        <v>1234</v>
+      </c>
+      <c r="C1235" t="s">
+        <v>2512</v>
+      </c>
+      <c r="D1235" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E1235" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1236">
+        <v>1235</v>
+      </c>
+      <c r="C1236" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D1236" t="s">
+        <v>2515</v>
+      </c>
+      <c r="E1236" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1237">
+        <v>1236</v>
+      </c>
+      <c r="C1237" t="s">
+        <v>2516</v>
+      </c>
+      <c r="D1237" t="s">
+        <v>2517</v>
+      </c>
+      <c r="E1237" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1238">
+        <v>1237</v>
+      </c>
+      <c r="C1238" t="s">
+        <v>2518</v>
+      </c>
+      <c r="D1238" t="s">
+        <v>2519</v>
+      </c>
+      <c r="E1238" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1239">
+        <v>1238</v>
+      </c>
+      <c r="C1239" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D1239" t="s">
+        <v>2521</v>
+      </c>
+      <c r="E1239" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1240">
+        <v>1239</v>
+      </c>
+      <c r="C1240" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D1240" t="s">
+        <v>2523</v>
+      </c>
+      <c r="E1240" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1241">
+        <v>1240</v>
+      </c>
+      <c r="C1241" t="s">
+        <v>2524</v>
+      </c>
+      <c r="D1241" t="s">
+        <v>2525</v>
+      </c>
+      <c r="E1241" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1242">
+        <v>1241</v>
+      </c>
+      <c r="C1242" t="s">
+        <v>2526</v>
+      </c>
+      <c r="D1242" t="s">
+        <v>2527</v>
+      </c>
+      <c r="E1242" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1243">
+        <v>1242</v>
+      </c>
+      <c r="C1243" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D1243" t="s">
+        <v>2529</v>
+      </c>
+      <c r="E1243" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1244">
+        <v>1243</v>
+      </c>
+      <c r="C1244" t="s">
+        <v>2530</v>
+      </c>
+      <c r="D1244" t="s">
+        <v>2531</v>
+      </c>
+      <c r="E1244" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1245">
+        <v>1244</v>
+      </c>
+      <c r="C1245" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D1245" t="s">
+        <v>2533</v>
+      </c>
+      <c r="E1245" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1246">
+        <v>1245</v>
+      </c>
+      <c r="C1246" t="s">
+        <v>2534</v>
+      </c>
+      <c r="D1246" t="s">
+        <v>2535</v>
+      </c>
+      <c r="E1246" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1247">
+        <v>1246</v>
+      </c>
+      <c r="C1247" t="s">
+        <v>2536</v>
+      </c>
+      <c r="D1247" t="s">
+        <v>2537</v>
+      </c>
+      <c r="E1247" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1248">
+        <v>1247</v>
+      </c>
+      <c r="C1248" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D1248" t="s">
+        <v>2539</v>
+      </c>
+      <c r="E1248" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1249">
+        <v>1248</v>
+      </c>
+      <c r="C1249" t="s">
+        <v>2540</v>
+      </c>
+      <c r="D1249" t="s">
+        <v>2541</v>
+      </c>
+      <c r="E1249" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1250">
+        <v>1249</v>
+      </c>
+      <c r="C1250" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D1250" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E1250" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1251">
+        <v>1250</v>
+      </c>
+      <c r="C1251" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D1251" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E1251" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1252">
+        <v>1251</v>
+      </c>
+      <c r="C1252" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D1252" t="s">
+        <v>2547</v>
+      </c>
+      <c r="E1252" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1253">
+        <v>1252</v>
+      </c>
+      <c r="C1253" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D1253" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E1253" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1254">
+        <v>1253</v>
+      </c>
+      <c r="C1254" t="s">
+        <v>2550</v>
+      </c>
+      <c r="D1254" t="s">
+        <v>2551</v>
+      </c>
+      <c r="E1254" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1255">
+        <v>1254</v>
+      </c>
+      <c r="C1255" t="s">
+        <v>2552</v>
+      </c>
+      <c r="D1255" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E1255" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1256">
+        <v>1255</v>
+      </c>
+      <c r="C1256" t="s">
+        <v>2554</v>
+      </c>
+      <c r="D1256" t="s">
+        <v>2555</v>
+      </c>
+      <c r="E1256" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1257">
+        <v>1256</v>
+      </c>
+      <c r="C1257" t="s">
+        <v>2556</v>
+      </c>
+      <c r="D1257" t="s">
+        <v>2557</v>
+      </c>
+      <c r="E1257" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1258">
+        <v>1257</v>
+      </c>
+      <c r="C1258" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D1258" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E1258" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1259">
+        <v>1258</v>
+      </c>
+      <c r="C1259" t="s">
+        <v>2560</v>
+      </c>
+      <c r="D1259" t="s">
+        <v>2561</v>
+      </c>
+      <c r="E1259" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1260">
+        <v>1259</v>
+      </c>
+      <c r="C1260" t="s">
+        <v>2562</v>
+      </c>
+      <c r="D1260" t="s">
+        <v>2563</v>
+      </c>
+      <c r="E1260" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1261">
+        <v>1260</v>
+      </c>
+      <c r="C1261" t="s">
+        <v>2564</v>
+      </c>
+      <c r="D1261" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E1261" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1262">
+        <v>1261</v>
+      </c>
+      <c r="C1262" t="s">
+        <v>2566</v>
+      </c>
+      <c r="D1262" t="s">
+        <v>2567</v>
+      </c>
+      <c r="E1262" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1263">
+        <v>1262</v>
+      </c>
+      <c r="C1263" t="s">
+        <v>2568</v>
+      </c>
+      <c r="D1263" t="s">
+        <v>2569</v>
+      </c>
+      <c r="E1263" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1264">
+        <v>1263</v>
+      </c>
+      <c r="C1264" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D1264" t="s">
+        <v>2571</v>
+      </c>
+      <c r="E1264" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1265">
+        <v>1264</v>
+      </c>
+      <c r="C1265" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D1265" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E1265" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1266">
+        <v>1265</v>
+      </c>
+      <c r="C1266" t="s">
+        <v>2574</v>
+      </c>
+      <c r="D1266" t="s">
+        <v>2575</v>
+      </c>
+      <c r="E1266" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1267">
+        <v>1266</v>
+      </c>
+      <c r="C1267" t="s">
+        <v>2576</v>
+      </c>
+      <c r="D1267" t="s">
+        <v>2577</v>
+      </c>
+      <c r="E1267" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1268" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1268">
+        <v>1267</v>
+      </c>
+      <c r="C1268" t="s">
+        <v>2578</v>
+      </c>
+      <c r="D1268" t="s">
+        <v>2579</v>
+      </c>
+      <c r="E1268" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1269" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1269">
+        <v>1268</v>
+      </c>
+      <c r="C1269" t="s">
+        <v>2580</v>
+      </c>
+      <c r="D1269" t="s">
+        <v>2581</v>
+      </c>
+      <c r="E1269" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1270" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1270">
+        <v>1269</v>
+      </c>
+      <c r="C1270" t="s">
+        <v>2582</v>
+      </c>
+      <c r="D1270" t="s">
+        <v>2583</v>
+      </c>
+      <c r="E1270" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1271" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1271">
+        <v>1270</v>
+      </c>
+      <c r="C1271" t="s">
+        <v>2584</v>
+      </c>
+      <c r="D1271" t="s">
+        <v>2585</v>
+      </c>
+      <c r="E1271" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1272" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1272">
+        <v>1271</v>
+      </c>
+      <c r="C1272" t="s">
+        <v>2586</v>
+      </c>
+      <c r="D1272" t="s">
+        <v>2587</v>
+      </c>
+      <c r="E1272" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1273" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1273">
+        <v>1272</v>
+      </c>
+      <c r="C1273" t="s">
+        <v>2588</v>
+      </c>
+      <c r="D1273" t="s">
+        <v>2589</v>
+      </c>
+      <c r="E1273" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1274" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1274">
+        <v>1273</v>
+      </c>
+      <c r="C1274" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1274" t="s">
+        <v>2591</v>
+      </c>
+      <c r="E1274" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1275" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1275">
+        <v>1274</v>
+      </c>
+      <c r="C1275" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1275" t="s">
+        <v>2592</v>
+      </c>
+      <c r="E1275" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1276" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1276">
+        <v>1275</v>
+      </c>
+      <c r="C1276" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1276" t="s">
+        <v>2593</v>
+      </c>
+      <c r="E1276" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1277" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1277">
+        <v>1276</v>
+      </c>
+      <c r="C1277" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1277" t="s">
+        <v>2594</v>
+      </c>
+      <c r="E1277" t="s">
+        <v>2470</v>
+      </c>
+    </row>
+    <row r="1278" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1278">
+        <v>1277</v>
+      </c>
+      <c r="C1278" t="s">
+        <v>2590</v>
+      </c>
+      <c r="D1278" t="s">
+        <v>2595</v>
+      </c>
+      <c r="E1278" t="s">
+        <v>2470</v>
       </c>
     </row>
   </sheetData>

--- a/FMS2025.xlsx
+++ b/FMS2025.xlsx
@@ -501,7 +501,7 @@
         <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="3">
@@ -542,7 +542,7 @@
         <v>6</v>
       </c>
       <c r="I3" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4">
@@ -583,7 +583,7 @@
         <v>9</v>
       </c>
       <c r="I4" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="5">
@@ -624,7 +624,7 @@
         <v>13</v>
       </c>
       <c r="I5" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="6">
@@ -665,7 +665,7 @@
         <v>4</v>
       </c>
       <c r="I6" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="7">
@@ -706,7 +706,7 @@
         <v>13</v>
       </c>
       <c r="I7" t="n">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="8">
@@ -747,7 +747,7 @@
         <v>3</v>
       </c>
       <c r="I8" t="n">
-        <v>5.5</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="9">
@@ -829,7 +829,7 @@
         <v>24</v>
       </c>
       <c r="I10" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="11">
@@ -870,7 +870,7 @@
         <v>36</v>
       </c>
       <c r="I11" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="12">
@@ -911,7 +911,7 @@
         <v>11</v>
       </c>
       <c r="I12" t="n">
-        <v>3.1</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="13">
@@ -993,7 +993,7 @@
         <v>12</v>
       </c>
       <c r="I14" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="15">
@@ -1034,7 +1034,7 @@
         <v>36</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="16">
@@ -1075,7 +1075,7 @@
         <v>47</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="17">
@@ -1116,7 +1116,7 @@
         <v>25</v>
       </c>
       <c r="I17" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
@@ -1157,7 +1157,7 @@
         <v>36</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="19">
@@ -1198,7 +1198,7 @@
         <v>21</v>
       </c>
       <c r="I19" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="20">
@@ -1239,7 +1239,7 @@
         <v>25</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="21">
@@ -1280,7 +1280,7 @@
         <v>25</v>
       </c>
       <c r="I21" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="22">
@@ -1321,7 +1321,7 @@
         <v>5</v>
       </c>
       <c r="I22" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="23">
@@ -1403,7 +1403,7 @@
         <v>8</v>
       </c>
       <c r="I24" t="n">
-        <v>3.6</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="25">
@@ -1444,7 +1444,7 @@
         <v>36</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="26">
@@ -1485,7 +1485,7 @@
         <v>40</v>
       </c>
       <c r="I26" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="27">
@@ -1567,7 +1567,7 @@
         <v>10</v>
       </c>
       <c r="I28" t="n">
-        <v>3.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="29">
@@ -1608,7 +1608,7 @@
         <v>48</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="30">
@@ -1649,7 +1649,7 @@
         <v>33</v>
       </c>
       <c r="I30" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="31">
@@ -1690,7 +1690,7 @@
         <v>16</v>
       </c>
       <c r="I31" t="n">
-        <v>2.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="32">
@@ -1731,7 +1731,7 @@
         <v>16</v>
       </c>
       <c r="I32" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="33">
@@ -1772,7 +1772,7 @@
         <v>31</v>
       </c>
       <c r="I33" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -1813,7 +1813,7 @@
         <v>43</v>
       </c>
       <c r="I34" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="35">
@@ -1854,7 +1854,7 @@
         <v>33</v>
       </c>
       <c r="I35" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="36">
@@ -1936,7 +1936,7 @@
         <v>45</v>
       </c>
       <c r="I37" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="38">
@@ -1977,7 +1977,7 @@
         <v>40</v>
       </c>
       <c r="I38" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2018,7 +2018,7 @@
         <v>43</v>
       </c>
       <c r="I39" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="40">
@@ -2059,7 +2059,7 @@
         <v>25</v>
       </c>
       <c r="I40" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="41">
@@ -2100,7 +2100,7 @@
         <v>19</v>
       </c>
       <c r="I41" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="42">
@@ -2141,7 +2141,7 @@
         <v>19</v>
       </c>
       <c r="I42" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="43">
@@ -2223,7 +2223,7 @@
         <v>51</v>
       </c>
       <c r="I44" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="45">
@@ -2264,7 +2264,7 @@
         <v>45</v>
       </c>
       <c r="I45" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="46">
@@ -2301,7 +2301,7 @@
         <v>18</v>
       </c>
       <c r="I46" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="47">
@@ -2342,7 +2342,7 @@
         <v>33</v>
       </c>
       <c r="I47" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="48">
@@ -2375,7 +2375,7 @@
         <v>21</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="49">
@@ -2416,7 +2416,7 @@
         <v>7</v>
       </c>
       <c r="I49" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="50">
@@ -2457,7 +2457,7 @@
         <v>31</v>
       </c>
       <c r="I50" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="51">
@@ -2498,7 +2498,7 @@
         <v>21</v>
       </c>
       <c r="I51" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="52">
@@ -2539,7 +2539,7 @@
         <v>1</v>
       </c>
       <c r="I52" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="53">
@@ -2580,7 +2580,7 @@
         <v>2</v>
       </c>
       <c r="I53" t="n">
-        <v>7.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="54">
@@ -2621,7 +2621,7 @@
         <v>1</v>
       </c>
       <c r="I54" t="n">
-        <v>8.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="55">
@@ -2662,7 +2662,7 @@
         <v>4</v>
       </c>
       <c r="I55" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="56">
@@ -2703,7 +2703,7 @@
         <v>12</v>
       </c>
       <c r="I56" t="n">
-        <v>3.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="57">
@@ -2744,7 +2744,7 @@
         <v>7</v>
       </c>
       <c r="I57" t="n">
-        <v>5.6</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="58">
@@ -2824,7 +2824,7 @@
         <v>6</v>
       </c>
       <c r="I59" t="n">
-        <v>6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="60">
@@ -2865,7 +2865,7 @@
         <v>8</v>
       </c>
       <c r="I60" t="n">
-        <v>4.8</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="61">
@@ -2906,7 +2906,7 @@
         <v>16</v>
       </c>
       <c r="I61" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="62">
@@ -2947,7 +2947,7 @@
         <v>10</v>
       </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="63">
@@ -2988,7 +2988,7 @@
         <v>9</v>
       </c>
       <c r="I63" t="n">
-        <v>4.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="64">
@@ -3101,7 +3101,7 @@
         <v>5</v>
       </c>
       <c r="I66" t="n">
-        <v>6.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="67">
@@ -3142,7 +3142,7 @@
         <v>17</v>
       </c>
       <c r="I67" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="68">
@@ -3183,7 +3183,7 @@
         <v>22</v>
       </c>
       <c r="I68" t="n">
-        <v>2.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="69">
@@ -3265,7 +3265,7 @@
         <v>14</v>
       </c>
       <c r="I70" t="n">
-        <v>3.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="71">
@@ -3386,7 +3386,7 @@
         <v>18</v>
       </c>
       <c r="I73" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="74">
@@ -3427,7 +3427,7 @@
         <v>15</v>
       </c>
       <c r="I74" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="75">
@@ -3507,7 +3507,7 @@
         <v>12</v>
       </c>
       <c r="I76" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="77">
@@ -3548,7 +3548,7 @@
         <v>9</v>
       </c>
       <c r="I77" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="78">
@@ -3589,7 +3589,7 @@
         <v>2</v>
       </c>
       <c r="I78" t="n">
-        <v>6.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="79">
@@ -3630,7 +3630,7 @@
         <v>10</v>
       </c>
       <c r="I79" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="80">
@@ -3712,7 +3712,7 @@
         <v>12</v>
       </c>
       <c r="I81" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="82">
@@ -3753,7 +3753,7 @@
         <v>5</v>
       </c>
       <c r="I82" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="83">
@@ -3835,7 +3835,7 @@
         <v>1</v>
       </c>
       <c r="I84" t="n">
-        <v>11</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="85">
@@ -3876,7 +3876,7 @@
         <v>3</v>
       </c>
       <c r="I85" t="n">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="86">
@@ -3917,7 +3917,7 @@
         <v>11</v>
       </c>
       <c r="I86" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="87">
@@ -3958,7 +3958,7 @@
         <v>13</v>
       </c>
       <c r="I87" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="88">
@@ -3999,7 +3999,7 @@
         <v>4</v>
       </c>
       <c r="I88" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="89">
@@ -4040,7 +4040,7 @@
         <v>7</v>
       </c>
       <c r="I89" t="n">
-        <v>4</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="90">
@@ -4122,7 +4122,7 @@
         <v>15</v>
       </c>
       <c r="I91" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="92">
@@ -4163,7 +4163,7 @@
         <v>20</v>
       </c>
       <c r="I92" t="n">
-        <v>0.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="93">
@@ -4204,7 +4204,7 @@
         <v>6</v>
       </c>
       <c r="I93" t="n">
-        <v>4.2</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="94">
@@ -4245,7 +4245,7 @@
         <v>18</v>
       </c>
       <c r="I94" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="95">
@@ -4282,7 +4282,7 @@
         <v>8</v>
       </c>
       <c r="I95" t="n">
-        <v>3.4</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="96">
@@ -4362,7 +4362,7 @@
         <v>4</v>
       </c>
       <c r="I97" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98">
@@ -4403,7 +4403,7 @@
         <v>1</v>
       </c>
       <c r="I98" t="n">
-        <v>7.7</v>
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="99">
@@ -4444,7 +4444,7 @@
         <v>20</v>
       </c>
       <c r="I99" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="100">
@@ -4485,7 +4485,7 @@
         <v>15</v>
       </c>
       <c r="I100" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="101">
@@ -4526,7 +4526,7 @@
         <v>5</v>
       </c>
       <c r="I101" t="n">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="102">
@@ -4567,7 +4567,7 @@
         <v>2</v>
       </c>
       <c r="I102" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="103">
@@ -4608,7 +4608,7 @@
         <v>11</v>
       </c>
       <c r="I103" t="n">
-        <v>3.7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="104">
@@ -4649,7 +4649,7 @@
         <v>7</v>
       </c>
       <c r="I104" t="n">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="105">
@@ -4690,7 +4690,7 @@
         <v>3</v>
       </c>
       <c r="I105" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="106">
@@ -4731,7 +4731,7 @@
         <v>21</v>
       </c>
       <c r="I106" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="107">
@@ -4772,7 +4772,7 @@
         <v>13</v>
       </c>
       <c r="I107" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="108">
@@ -4852,7 +4852,7 @@
         <v>10</v>
       </c>
       <c r="I109" t="n">
-        <v>3.9</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="110">
@@ -4893,7 +4893,7 @@
         <v>17</v>
       </c>
       <c r="I110" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="111">
@@ -4934,7 +4934,7 @@
         <v>5</v>
       </c>
       <c r="I111" t="n">
-        <v>5.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="112">
@@ -4975,7 +4975,7 @@
         <v>21</v>
       </c>
       <c r="I112" t="n">
-        <v>2.2</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="113">
@@ -5016,7 +5016,7 @@
         <v>9</v>
       </c>
       <c r="I113" t="n">
-        <v>4.4</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="114">
@@ -5057,7 +5057,7 @@
         <v>8</v>
       </c>
       <c r="I114" t="n">
-        <v>4.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="115">
@@ -5178,7 +5178,7 @@
         <v>13</v>
       </c>
       <c r="I117" t="n">
-        <v>3.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="118">
@@ -5219,7 +5219,7 @@
         <v>16</v>
       </c>
       <c r="I118" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="119">
@@ -5260,7 +5260,7 @@
         <v>2</v>
       </c>
       <c r="I119" t="n">
-        <v>6.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="120">
@@ -5301,7 +5301,7 @@
         <v>3</v>
       </c>
       <c r="I120" t="n">
-        <v>5.1</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="121">
@@ -5342,7 +5342,7 @@
         <v>4</v>
       </c>
       <c r="I121" t="n">
-        <v>4.9</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="122">
@@ -5383,7 +5383,7 @@
         <v>4</v>
       </c>
       <c r="I122" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="123">
@@ -5424,7 +5424,7 @@
         <v>25</v>
       </c>
       <c r="I123" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="124">
@@ -5465,7 +5465,7 @@
         <v>20</v>
       </c>
       <c r="I124" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="125">
@@ -5545,7 +5545,7 @@
         <v>1</v>
       </c>
       <c r="I126" t="n">
-        <v>10</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="127">
@@ -5586,7 +5586,7 @@
         <v>15</v>
       </c>
       <c r="I127" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="128">
@@ -5627,7 +5627,7 @@
         <v>23</v>
       </c>
       <c r="I128" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="129">
@@ -5668,7 +5668,7 @@
         <v>20</v>
       </c>
       <c r="I129" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="130">
@@ -5709,7 +5709,7 @@
         <v>12</v>
       </c>
       <c r="I130" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="131">
@@ -5750,7 +5750,7 @@
         <v>17</v>
       </c>
       <c r="I131" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="132">
@@ -5791,7 +5791,7 @@
         <v>7</v>
       </c>
       <c r="I132" t="n">
-        <v>3.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="133">
@@ -5832,7 +5832,7 @@
         <v>29</v>
       </c>
       <c r="I133" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="134">
@@ -5873,7 +5873,7 @@
         <v>18</v>
       </c>
       <c r="I134" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="135">
@@ -5914,7 +5914,7 @@
         <v>29</v>
       </c>
       <c r="I135" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="136">
@@ -5955,7 +5955,7 @@
         <v>38</v>
       </c>
       <c r="I136" t="n">
-        <v>1.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="137">
@@ -5996,7 +5996,7 @@
         <v>18</v>
       </c>
       <c r="I137" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="138">
@@ -6029,7 +6029,7 @@
         <v>40</v>
       </c>
       <c r="I138" t="n">
-        <v>1.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="139">
@@ -6070,7 +6070,7 @@
         <v>8</v>
       </c>
       <c r="I139" t="n">
-        <v>3.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="140">
@@ -6111,7 +6111,7 @@
         <v>37</v>
       </c>
       <c r="I140" t="n">
-        <v>1.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="141">
@@ -6152,7 +6152,7 @@
         <v>23</v>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="142">
@@ -6193,7 +6193,7 @@
         <v>12</v>
       </c>
       <c r="I142" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="143">
@@ -6234,7 +6234,7 @@
         <v>29</v>
       </c>
       <c r="I143" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="144">
@@ -6275,7 +6275,7 @@
         <v>35</v>
       </c>
       <c r="I144" t="n">
-        <v>1.9</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="145">
@@ -6316,7 +6316,7 @@
         <v>35</v>
       </c>
       <c r="I145" t="n">
-        <v>1.9</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="146">
@@ -6357,7 +6357,7 @@
         <v>8</v>
       </c>
       <c r="I146" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="147">
@@ -6398,7 +6398,7 @@
         <v>25</v>
       </c>
       <c r="I147" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="148">
@@ -6439,7 +6439,7 @@
         <v>4</v>
       </c>
       <c r="I148" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="149">
@@ -6480,7 +6480,7 @@
         <v>29</v>
       </c>
       <c r="I149" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="150">
@@ -6560,7 +6560,7 @@
         <v>29</v>
       </c>
       <c r="I151" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="152">
@@ -6601,7 +6601,7 @@
         <v>16</v>
       </c>
       <c r="I152" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="153">
@@ -6642,7 +6642,7 @@
         <v>10</v>
       </c>
       <c r="I153" t="n">
-        <v>3.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="154">
@@ -6724,7 +6724,7 @@
         <v>34</v>
       </c>
       <c r="I155" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="156">
@@ -6765,7 +6765,7 @@
         <v>41</v>
       </c>
       <c r="I156" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="157">
@@ -6798,7 +6798,7 @@
         <v>27</v>
       </c>
       <c r="I157" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="158">
@@ -6839,7 +6839,7 @@
         <v>20</v>
       </c>
       <c r="I158" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="159">
@@ -6911,7 +6911,7 @@
         <v>38</v>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="161">
@@ -6952,7 +6952,7 @@
         <v>10</v>
       </c>
       <c r="I161" t="n">
-        <v>3.2</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="162">
@@ -6993,7 +6993,7 @@
         <v>1</v>
       </c>
       <c r="I162" t="n">
-        <v>9</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="163">
@@ -7034,7 +7034,7 @@
         <v>2</v>
       </c>
       <c r="I163" t="n">
-        <v>8.800000000000001</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="164">
@@ -7075,7 +7075,7 @@
         <v>4</v>
       </c>
       <c r="I164" t="n">
-        <v>5.8</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="165">
@@ -7116,7 +7116,7 @@
         <v>22</v>
       </c>
       <c r="I165" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="166">
@@ -7157,7 +7157,7 @@
         <v>8</v>
       </c>
       <c r="I166" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="167">
@@ -7198,7 +7198,7 @@
         <v>20</v>
       </c>
       <c r="I167" t="n">
-        <v>2.9</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="168">
@@ -7280,7 +7280,7 @@
         <v>10</v>
       </c>
       <c r="I169" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="170">
@@ -7321,7 +7321,7 @@
         <v>3</v>
       </c>
       <c r="I170" t="n">
-        <v>6.1</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="171">
@@ -7362,7 +7362,7 @@
         <v>29</v>
       </c>
       <c r="I171" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="172">
@@ -7403,7 +7403,7 @@
         <v>36</v>
       </c>
       <c r="I172" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="173">
@@ -7444,7 +7444,7 @@
         <v>7</v>
       </c>
       <c r="I173" t="n">
-        <v>4.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="174">
@@ -7485,7 +7485,7 @@
         <v>5</v>
       </c>
       <c r="I174" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="175">
@@ -7526,7 +7526,7 @@
         <v>24</v>
       </c>
       <c r="I175" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="176">
@@ -7567,7 +7567,7 @@
         <v>9</v>
       </c>
       <c r="I176" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="177">
@@ -7608,7 +7608,7 @@
         <v>11</v>
       </c>
       <c r="I177" t="n">
-        <v>3.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="178">
@@ -7649,7 +7649,7 @@
         <v>24</v>
       </c>
       <c r="I178" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179">
@@ -7690,7 +7690,7 @@
         <v>36</v>
       </c>
       <c r="I179" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="180">
@@ -7731,7 +7731,7 @@
         <v>31</v>
       </c>
       <c r="I180" t="n">
-        <v>2.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="181">
@@ -7772,7 +7772,7 @@
         <v>46</v>
       </c>
       <c r="I181" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="182">
@@ -7813,7 +7813,7 @@
         <v>12</v>
       </c>
       <c r="I182" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="183">
@@ -7854,7 +7854,7 @@
         <v>29</v>
       </c>
       <c r="I183" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="184">
@@ -7895,7 +7895,7 @@
         <v>33</v>
       </c>
       <c r="I184" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="185">
@@ -7936,7 +7936,7 @@
         <v>12</v>
       </c>
       <c r="I185" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="186">
@@ -7977,7 +7977,7 @@
         <v>16</v>
       </c>
       <c r="I186" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="187">
@@ -8018,7 +8018,7 @@
         <v>42</v>
       </c>
       <c r="I187" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="188">
@@ -8051,7 +8051,7 @@
         <v>24</v>
       </c>
       <c r="I188" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="189">
@@ -8092,7 +8092,7 @@
         <v>15</v>
       </c>
       <c r="I189" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="190">
@@ -8133,7 +8133,7 @@
         <v>16</v>
       </c>
       <c r="I190" t="n">
-        <v>3.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="191">
@@ -8174,7 +8174,7 @@
         <v>24</v>
       </c>
       <c r="I191" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="192">
@@ -8215,7 +8215,7 @@
         <v>38</v>
       </c>
       <c r="I192" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="193">
@@ -8256,7 +8256,7 @@
         <v>42</v>
       </c>
       <c r="I193" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="194">
@@ -8338,7 +8338,7 @@
         <v>22</v>
       </c>
       <c r="I195" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="196">
@@ -8379,7 +8379,7 @@
         <v>6</v>
       </c>
       <c r="I196" t="n">
-        <v>4.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="197">
@@ -8420,7 +8420,7 @@
         <v>12</v>
       </c>
       <c r="I197" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="198">
@@ -8461,7 +8461,7 @@
         <v>42</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="199">
@@ -8502,7 +8502,7 @@
         <v>42</v>
       </c>
       <c r="I199" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="200">
@@ -8543,7 +8543,7 @@
         <v>40</v>
       </c>
       <c r="I200" t="n">
-        <v>1.8</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="201">
@@ -8584,7 +8584,7 @@
         <v>16</v>
       </c>
       <c r="I201" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="202">
@@ -8625,7 +8625,7 @@
         <v>33</v>
       </c>
       <c r="I202" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="203">
@@ -8666,7 +8666,7 @@
         <v>39</v>
       </c>
       <c r="I203" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="204">
@@ -8707,7 +8707,7 @@
         <v>21</v>
       </c>
       <c r="I204" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="205">
@@ -8748,7 +8748,7 @@
         <v>33</v>
       </c>
       <c r="I205" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="206">
@@ -8789,7 +8789,7 @@
         <v>19</v>
       </c>
       <c r="I206" t="n">
-        <v>3</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="207">
@@ -8830,7 +8830,7 @@
         <v>49</v>
       </c>
       <c r="I207" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="208">
@@ -8871,7 +8871,7 @@
         <v>31</v>
       </c>
       <c r="I208" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="209">
@@ -8951,7 +8951,7 @@
         <v>46</v>
       </c>
       <c r="I210" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="211">
@@ -8992,7 +8992,7 @@
         <v>50</v>
       </c>
       <c r="I211" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="212">
@@ -9033,7 +9033,7 @@
         <v>24</v>
       </c>
       <c r="I212" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="213">
@@ -9074,7 +9074,7 @@
         <v>41</v>
       </c>
       <c r="I213" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="214">
@@ -9154,7 +9154,7 @@
         <v>3</v>
       </c>
       <c r="I215" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="216">
@@ -9195,7 +9195,7 @@
         <v>8</v>
       </c>
       <c r="I216" t="n">
-        <v>4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="217">
@@ -9277,7 +9277,7 @@
         <v>2</v>
       </c>
       <c r="I218" t="n">
-        <v>6.4</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="219">
@@ -9318,7 +9318,7 @@
         <v>14</v>
       </c>
       <c r="I219" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="220">
@@ -9359,7 +9359,7 @@
         <v>13</v>
       </c>
       <c r="I220" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="221">
@@ -9441,7 +9441,7 @@
         <v>1</v>
       </c>
       <c r="I222" t="n">
-        <v>10.7</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="223">
@@ -9482,7 +9482,7 @@
         <v>22</v>
       </c>
       <c r="I223" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="224">
@@ -9523,7 +9523,7 @@
         <v>17</v>
       </c>
       <c r="I224" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="225">
@@ -9564,7 +9564,7 @@
         <v>22</v>
       </c>
       <c r="I225" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="226">
@@ -9605,7 +9605,7 @@
         <v>17</v>
       </c>
       <c r="I226" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="227">
@@ -9646,7 +9646,7 @@
         <v>34</v>
       </c>
       <c r="I227" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="228">
@@ -9728,7 +9728,7 @@
         <v>6</v>
       </c>
       <c r="I229" t="n">
-        <v>4.7</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="230">
@@ -9769,7 +9769,7 @@
         <v>10</v>
       </c>
       <c r="I230" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="231">
@@ -9851,7 +9851,7 @@
         <v>5</v>
       </c>
       <c r="I232" t="n">
-        <v>5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="233">
@@ -9892,7 +9892,7 @@
         <v>21</v>
       </c>
       <c r="I233" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="234">
@@ -9933,7 +9933,7 @@
         <v>11</v>
       </c>
       <c r="I234" t="n">
-        <v>3.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="235">
@@ -9974,7 +9974,7 @@
         <v>29</v>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="236">
@@ -10056,7 +10056,7 @@
         <v>25</v>
       </c>
       <c r="I237" t="n">
-        <v>1.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="238">
@@ -10138,7 +10138,7 @@
         <v>4</v>
       </c>
       <c r="I239" t="n">
-        <v>5.5</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="240">
@@ -10179,7 +10179,7 @@
         <v>12</v>
       </c>
       <c r="I240" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="241">
@@ -10220,7 +10220,7 @@
         <v>24</v>
       </c>
       <c r="I241" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="242">
@@ -10261,7 +10261,7 @@
         <v>20</v>
       </c>
       <c r="I242" t="n">
-        <v>1.7</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="243">
@@ -10302,7 +10302,7 @@
         <v>25</v>
       </c>
       <c r="I243" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="244">
@@ -10343,7 +10343,7 @@
         <v>9</v>
       </c>
       <c r="I244" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="245">
@@ -10425,7 +10425,7 @@
         <v>14</v>
       </c>
       <c r="I246" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="247">
@@ -10507,7 +10507,7 @@
         <v>14</v>
       </c>
       <c r="I248" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="249">
@@ -10548,7 +10548,7 @@
         <v>12</v>
       </c>
       <c r="I249" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="250">
@@ -10589,7 +10589,7 @@
         <v>10</v>
       </c>
       <c r="I250" t="n">
-        <v>4.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="251">
@@ -10630,7 +10630,7 @@
         <v>15</v>
       </c>
       <c r="I251" t="n">
-        <v>3.8</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="252">
@@ -10671,7 +10671,7 @@
         <v>4</v>
       </c>
       <c r="I252" t="n">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="253">
@@ -10712,7 +10712,7 @@
         <v>5</v>
       </c>
       <c r="I253" t="n">
-        <v>6.3</v>
+        <v>10.4</v>
       </c>
     </row>
     <row r="254">
@@ -10753,7 +10753,7 @@
         <v>7</v>
       </c>
       <c r="I254" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="255">
@@ -10833,7 +10833,7 @@
         <v>42</v>
       </c>
       <c r="I256" t="n">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="257">
@@ -10874,7 +10874,7 @@
         <v>19</v>
       </c>
       <c r="I257" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="258">
@@ -10915,7 +10915,7 @@
         <v>32</v>
       </c>
       <c r="I258" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="259">
@@ -10995,7 +10995,7 @@
         <v>46</v>
       </c>
       <c r="I260" t="n">
-        <v>1.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="261">
@@ -11036,7 +11036,7 @@
         <v>1</v>
       </c>
       <c r="I261" t="n">
-        <v>9.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="262">
@@ -11116,7 +11116,7 @@
         <v>9</v>
       </c>
       <c r="I263" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="264">
@@ -11157,7 +11157,7 @@
         <v>8</v>
       </c>
       <c r="I264" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="265">
@@ -11198,7 +11198,7 @@
         <v>27</v>
       </c>
       <c r="I265" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="266">
@@ -11239,7 +11239,7 @@
         <v>38</v>
       </c>
       <c r="I266" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="267">
@@ -11321,7 +11321,7 @@
         <v>28</v>
       </c>
       <c r="I268" t="n">
-        <v>2.6</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="269">
@@ -11403,7 +11403,7 @@
         <v>30</v>
       </c>
       <c r="I270" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="271">
@@ -11444,7 +11444,7 @@
         <v>47</v>
       </c>
       <c r="I271" t="n">
-        <v>1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="272">
@@ -11526,7 +11526,7 @@
         <v>39</v>
       </c>
       <c r="I273" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="274">
@@ -11567,7 +11567,7 @@
         <v>36</v>
       </c>
       <c r="I274" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="275">
@@ -11608,7 +11608,7 @@
         <v>12</v>
       </c>
       <c r="I275" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="276">
@@ -11729,7 +11729,7 @@
         <v>19</v>
       </c>
       <c r="I278" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="279">
@@ -11770,7 +11770,7 @@
         <v>11</v>
       </c>
       <c r="I279" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="280">
@@ -11811,7 +11811,7 @@
         <v>35</v>
       </c>
       <c r="I280" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="281">
@@ -11893,7 +11893,7 @@
         <v>41</v>
       </c>
       <c r="I282" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="283">
@@ -12008,7 +12008,7 @@
         <v>40</v>
       </c>
       <c r="I285" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="286">
@@ -12049,7 +12049,7 @@
         <v>21</v>
       </c>
       <c r="I286" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="287">
@@ -12090,7 +12090,7 @@
         <v>12</v>
       </c>
       <c r="I287" t="n">
-        <v>4</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="288">
@@ -12209,7 +12209,7 @@
         <v>6</v>
       </c>
       <c r="I290" t="n">
-        <v>6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="291">
@@ -12250,7 +12250,7 @@
         <v>42</v>
       </c>
       <c r="I291" t="n">
-        <v>1.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="292">
@@ -12291,7 +12291,7 @@
         <v>42</v>
       </c>
       <c r="I292" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="293">
@@ -12332,7 +12332,7 @@
         <v>23</v>
       </c>
       <c r="I293" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="294">
@@ -12373,7 +12373,7 @@
         <v>16</v>
       </c>
       <c r="I294" t="n">
-        <v>3.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="295">
@@ -12414,7 +12414,7 @@
         <v>24</v>
       </c>
       <c r="I295" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="296">
@@ -12494,7 +12494,7 @@
         <v>36</v>
       </c>
       <c r="I297" t="n">
-        <v>2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="298">
@@ -12535,7 +12535,7 @@
         <v>2</v>
       </c>
       <c r="I298" t="n">
-        <v>8.199999999999999</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="299">
@@ -12572,7 +12572,7 @@
         <v>18</v>
       </c>
       <c r="I299" t="n">
-        <v>3.6</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="300">
@@ -12613,7 +12613,7 @@
         <v>25</v>
       </c>
       <c r="I300" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="301">
@@ -12654,7 +12654,7 @@
         <v>22</v>
       </c>
       <c r="I301" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="302">
@@ -12734,7 +12734,7 @@
         <v>3</v>
       </c>
       <c r="I303" t="n">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="304">
@@ -12847,7 +12847,7 @@
         <v>50</v>
       </c>
       <c r="I306" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="307">
@@ -13089,7 +13089,7 @@
         <v>28</v>
       </c>
       <c r="I312" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="313">
@@ -13130,7 +13130,7 @@
         <v>12</v>
       </c>
       <c r="I313" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="314">
@@ -13171,7 +13171,7 @@
         <v>2</v>
       </c>
       <c r="I314" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="315">
@@ -13212,7 +13212,7 @@
         <v>10</v>
       </c>
       <c r="I315" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="316">
@@ -13253,7 +13253,7 @@
         <v>4</v>
       </c>
       <c r="I316" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="317">
@@ -13294,7 +13294,7 @@
         <v>22</v>
       </c>
       <c r="I317" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="318">
@@ -13335,7 +13335,7 @@
         <v>13</v>
       </c>
       <c r="I318" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="319">
@@ -13376,7 +13376,7 @@
         <v>18</v>
       </c>
       <c r="I319" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="320">
@@ -13458,7 +13458,7 @@
         <v>1</v>
       </c>
       <c r="I321" t="n">
-        <v>7</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="322">
@@ -13499,7 +13499,7 @@
         <v>9</v>
       </c>
       <c r="I322" t="n">
-        <v>3.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="323">
@@ -13540,7 +13540,7 @@
         <v>14</v>
       </c>
       <c r="I323" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="324">
@@ -13581,7 +13581,7 @@
         <v>17</v>
       </c>
       <c r="I324" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="325">
@@ -13622,7 +13622,7 @@
         <v>18</v>
       </c>
       <c r="I325" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="326">
@@ -13663,7 +13663,7 @@
         <v>23</v>
       </c>
       <c r="I326" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="327">
@@ -13704,7 +13704,7 @@
         <v>28</v>
       </c>
       <c r="I327" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="328">
@@ -13745,7 +13745,7 @@
         <v>28</v>
       </c>
       <c r="I328" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="329">
@@ -13827,7 +13827,7 @@
         <v>7</v>
       </c>
       <c r="I330" t="n">
-        <v>3.4</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="331">
@@ -13868,7 +13868,7 @@
         <v>39</v>
       </c>
       <c r="I331" t="n">
-        <v>0.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="332">
@@ -13991,7 +13991,7 @@
         <v>23</v>
       </c>
       <c r="I334" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="335">
@@ -14032,7 +14032,7 @@
         <v>14</v>
       </c>
       <c r="I335" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="336">
@@ -14270,7 +14270,7 @@
         <v>18</v>
       </c>
       <c r="I341" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="342">
@@ -14311,7 +14311,7 @@
         <v>14</v>
       </c>
       <c r="I342" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="343">
@@ -14432,7 +14432,7 @@
         <v>18</v>
       </c>
       <c r="I345" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="346">
@@ -14512,7 +14512,7 @@
         <v>26</v>
       </c>
       <c r="I347" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="348">
@@ -14553,7 +14553,7 @@
         <v>28</v>
       </c>
       <c r="I348" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="349">
@@ -14594,7 +14594,7 @@
         <v>7</v>
       </c>
       <c r="I349" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="350">
@@ -14635,7 +14635,7 @@
         <v>8</v>
       </c>
       <c r="I350" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="351">
@@ -14676,7 +14676,7 @@
         <v>14</v>
       </c>
       <c r="I351" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="352">
@@ -14709,7 +14709,7 @@
         <v>1</v>
       </c>
       <c r="I352" t="n">
-        <v>14.5</v>
+        <v>12.7</v>
       </c>
     </row>
     <row r="353">
@@ -14750,7 +14750,7 @@
         <v>4</v>
       </c>
       <c r="I353" t="n">
-        <v>8.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="354">
@@ -14791,7 +14791,7 @@
         <v>8</v>
       </c>
       <c r="I354" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="355">
@@ -14832,7 +14832,7 @@
         <v>12</v>
       </c>
       <c r="I355" t="n">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="356">
@@ -14873,7 +14873,7 @@
         <v>2</v>
       </c>
       <c r="I356" t="n">
-        <v>9.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="357">
@@ -14914,7 +14914,7 @@
         <v>5</v>
       </c>
       <c r="I357" t="n">
-        <v>7.9</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="358">
@@ -14955,7 +14955,7 @@
         <v>6</v>
       </c>
       <c r="I358" t="n">
-        <v>7.7</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="359">
@@ -14996,7 +14996,7 @@
         <v>3</v>
       </c>
       <c r="I359" t="n">
-        <v>8.800000000000001</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="360">
@@ -15037,7 +15037,7 @@
         <v>15</v>
       </c>
       <c r="I360" t="n">
-        <v>4.4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="361">
@@ -15078,7 +15078,7 @@
         <v>27</v>
       </c>
       <c r="I361" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="362">
@@ -15119,7 +15119,7 @@
         <v>13</v>
       </c>
       <c r="I362" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="363">
@@ -15160,7 +15160,7 @@
         <v>28</v>
       </c>
       <c r="I363" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="364">
@@ -15197,7 +15197,7 @@
         <v>18</v>
       </c>
       <c r="I364" t="n">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="365">
@@ -15238,7 +15238,7 @@
         <v>26</v>
       </c>
       <c r="I365" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="366">
@@ -15316,7 +15316,7 @@
         <v>18</v>
       </c>
       <c r="I367" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="368">
@@ -15357,7 +15357,7 @@
         <v>32</v>
       </c>
       <c r="I368" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="369">
@@ -15390,7 +15390,7 @@
         <v>11</v>
       </c>
       <c r="I369" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="370">
@@ -15427,7 +15427,7 @@
         <v>20</v>
       </c>
       <c r="I370" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="371">
@@ -15468,7 +15468,7 @@
         <v>22</v>
       </c>
       <c r="I371" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="372">
@@ -15509,7 +15509,7 @@
         <v>24</v>
       </c>
       <c r="I372" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="373">
@@ -15550,7 +15550,7 @@
         <v>20</v>
       </c>
       <c r="I373" t="n">
-        <v>3.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="374">
@@ -15591,7 +15591,7 @@
         <v>16</v>
       </c>
       <c r="I374" t="n">
-        <v>4.2</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="375">
@@ -15632,7 +15632,7 @@
         <v>17</v>
       </c>
       <c r="I375" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="376">
@@ -15669,7 +15669,7 @@
         <v>30</v>
       </c>
       <c r="I376" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="377">
@@ -15710,7 +15710,7 @@
         <v>29</v>
       </c>
       <c r="I377" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="378">
@@ -15751,7 +15751,7 @@
         <v>34</v>
       </c>
       <c r="I378" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="379">
@@ -15792,7 +15792,7 @@
         <v>33</v>
       </c>
       <c r="I379" t="n">
-        <v>1.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="380">
@@ -15833,7 +15833,7 @@
         <v>22</v>
       </c>
       <c r="I380" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="381">
@@ -15874,7 +15874,7 @@
         <v>30</v>
       </c>
       <c r="I381" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="382">
@@ -15915,7 +15915,7 @@
         <v>25</v>
       </c>
       <c r="I382" t="n">
-        <v>3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="383">
@@ -15956,7 +15956,7 @@
         <v>10</v>
       </c>
       <c r="I383" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="384">
@@ -15997,7 +15997,7 @@
         <v>2</v>
       </c>
       <c r="I384" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="385">
@@ -16038,7 +16038,7 @@
         <v>16</v>
       </c>
       <c r="I385" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="386">
@@ -16079,7 +16079,7 @@
         <v>3</v>
       </c>
       <c r="I386" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="387">
@@ -16120,7 +16120,7 @@
         <v>19</v>
       </c>
       <c r="I387" t="n">
-        <v>0.9</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="388">
@@ -16161,7 +16161,7 @@
         <v>10</v>
       </c>
       <c r="I388" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="389">
@@ -16202,7 +16202,7 @@
         <v>7</v>
       </c>
       <c r="I389" t="n">
-        <v>3.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="390">
@@ -16243,7 +16243,7 @@
         <v>12</v>
       </c>
       <c r="I390" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="391">
@@ -16284,7 +16284,7 @@
         <v>15</v>
       </c>
       <c r="I391" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="392">
@@ -16325,7 +16325,7 @@
         <v>1</v>
       </c>
       <c r="I392" t="n">
-        <v>8.1</v>
+        <v>13</v>
       </c>
     </row>
     <row r="393">
@@ -16366,7 +16366,7 @@
         <v>8</v>
       </c>
       <c r="I393" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="394">
@@ -16446,7 +16446,7 @@
         <v>17</v>
       </c>
       <c r="I395" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="396">
@@ -16526,7 +16526,7 @@
         <v>11</v>
       </c>
       <c r="I397" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="398">
@@ -16567,7 +16567,7 @@
         <v>4</v>
       </c>
       <c r="I398" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="399">
@@ -16608,7 +16608,7 @@
         <v>18</v>
       </c>
       <c r="I399" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="400">
@@ -16649,7 +16649,7 @@
         <v>19</v>
       </c>
       <c r="I400" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="401">
@@ -16690,7 +16690,7 @@
         <v>12</v>
       </c>
       <c r="I401" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="402">
@@ -16731,7 +16731,7 @@
         <v>14</v>
       </c>
       <c r="I402" t="n">
-        <v>2.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="403">
@@ -16772,7 +16772,7 @@
         <v>4</v>
       </c>
       <c r="I403" t="n">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="404">
@@ -16813,7 +16813,7 @@
         <v>8</v>
       </c>
       <c r="I404" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="405">
@@ -16854,7 +16854,7 @@
         <v>4</v>
       </c>
       <c r="I405" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="406">
@@ -16895,7 +16895,7 @@
         <v>3</v>
       </c>
       <c r="I406" t="n">
-        <v>9.5</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="407">
@@ -16936,7 +16936,7 @@
         <v>31</v>
       </c>
       <c r="I407" t="n">
-        <v>2.8</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="408">
@@ -16977,7 +16977,7 @@
         <v>1</v>
       </c>
       <c r="I408" t="n">
-        <v>12</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="409">
@@ -17018,7 +17018,7 @@
         <v>4</v>
       </c>
       <c r="I409" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="410">
@@ -17059,7 +17059,7 @@
         <v>14</v>
       </c>
       <c r="I410" t="n">
-        <v>5.4</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="411">
@@ -17100,7 +17100,7 @@
         <v>29</v>
       </c>
       <c r="I411" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="412">
@@ -17141,7 +17141,7 @@
         <v>61</v>
       </c>
       <c r="I412" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="413">
@@ -17223,7 +17223,7 @@
         <v>6</v>
       </c>
       <c r="I414" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="415">
@@ -17264,7 +17264,7 @@
         <v>10</v>
       </c>
       <c r="I415" t="n">
-        <v>6</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="416">
@@ -17305,7 +17305,7 @@
         <v>42</v>
       </c>
       <c r="I416" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="417">
@@ -17346,7 +17346,7 @@
         <v>2</v>
       </c>
       <c r="I417" t="n">
-        <v>9.800000000000001</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="418">
@@ -17387,7 +17387,7 @@
         <v>23</v>
       </c>
       <c r="I418" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="419">
@@ -17424,7 +17424,7 @@
         <v>20</v>
       </c>
       <c r="I419" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="420">
@@ -17465,7 +17465,7 @@
         <v>11</v>
       </c>
       <c r="I420" t="n">
-        <v>5.9</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="421">
@@ -17506,7 +17506,7 @@
         <v>38</v>
       </c>
       <c r="I421" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="422">
@@ -17547,7 +17547,7 @@
         <v>42</v>
       </c>
       <c r="I422" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="423">
@@ -17588,7 +17588,7 @@
         <v>24</v>
       </c>
       <c r="I423" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="424">
@@ -17629,7 +17629,7 @@
         <v>48</v>
       </c>
       <c r="I424" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="425">
@@ -17670,7 +17670,7 @@
         <v>48</v>
       </c>
       <c r="I425" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="426">
@@ -17711,7 +17711,7 @@
         <v>21</v>
       </c>
       <c r="I426" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="427">
@@ -17752,7 +17752,7 @@
         <v>40</v>
       </c>
       <c r="I427" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="428">
@@ -17793,7 +17793,7 @@
         <v>27</v>
       </c>
       <c r="I428" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="429">
@@ -17834,7 +17834,7 @@
         <v>57</v>
       </c>
       <c r="I429" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="430">
@@ -17875,7 +17875,7 @@
         <v>74</v>
       </c>
       <c r="I430" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -17916,7 +17916,7 @@
         <v>56</v>
       </c>
       <c r="I431" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="432">
@@ -17957,7 +17957,7 @@
         <v>38</v>
       </c>
       <c r="I432" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="433">
@@ -17998,7 +17998,7 @@
         <v>61</v>
       </c>
       <c r="I433" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="434">
@@ -18039,7 +18039,7 @@
         <v>59</v>
       </c>
       <c r="I434" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="435">
@@ -18080,7 +18080,7 @@
         <v>42</v>
       </c>
       <c r="I435" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="436">
@@ -18121,7 +18121,7 @@
         <v>48</v>
       </c>
       <c r="I436" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="437">
@@ -18203,7 +18203,7 @@
         <v>76</v>
       </c>
       <c r="I438" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="439">
@@ -18244,7 +18244,7 @@
         <v>16</v>
       </c>
       <c r="I439" t="n">
-        <v>5.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="440">
@@ -18281,7 +18281,7 @@
         <v>34</v>
       </c>
       <c r="I440" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="441">
@@ -18361,7 +18361,7 @@
         <v>5</v>
       </c>
       <c r="I442" t="n">
-        <v>7.6</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="443">
@@ -18398,7 +18398,7 @@
         <v>17</v>
       </c>
       <c r="I443" t="n">
-        <v>4.9</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="444">
@@ -18439,7 +18439,7 @@
         <v>36</v>
       </c>
       <c r="I444" t="n">
-        <v>2.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="445">
@@ -18480,7 +18480,7 @@
         <v>19</v>
       </c>
       <c r="I445" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="446">
@@ -18521,7 +18521,7 @@
         <v>40</v>
       </c>
       <c r="I446" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="447">
@@ -18562,7 +18562,7 @@
         <v>7</v>
       </c>
       <c r="I447" t="n">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="448">
@@ -18599,7 +18599,7 @@
         <v>53</v>
       </c>
       <c r="I448" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="449">
@@ -18679,7 +18679,7 @@
         <v>52</v>
       </c>
       <c r="I450" t="n">
-        <v>1.9</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="451">
@@ -18720,7 +18720,7 @@
         <v>27</v>
       </c>
       <c r="I451" t="n">
-        <v>3.3</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="452">
@@ -18761,7 +18761,7 @@
         <v>69</v>
       </c>
       <c r="I452" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="453">
@@ -18802,7 +18802,7 @@
         <v>13</v>
       </c>
       <c r="I453" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="454">
@@ -18843,7 +18843,7 @@
         <v>59</v>
       </c>
       <c r="I454" t="n">
-        <v>1.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="455">
@@ -18884,7 +18884,7 @@
         <v>31</v>
       </c>
       <c r="I455" t="n">
-        <v>2.8</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="456">
@@ -18925,7 +18925,7 @@
         <v>79</v>
       </c>
       <c r="I456" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="457">
@@ -18966,7 +18966,7 @@
         <v>12</v>
       </c>
       <c r="I457" t="n">
-        <v>5.6</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="458">
@@ -19007,7 +19007,7 @@
         <v>34</v>
       </c>
       <c r="I458" t="n">
-        <v>2.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="459">
@@ -19048,7 +19048,7 @@
         <v>61</v>
       </c>
       <c r="I459" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="460">
@@ -19089,7 +19089,7 @@
         <v>68</v>
       </c>
       <c r="I460" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="461">
@@ -19130,7 +19130,7 @@
         <v>76</v>
       </c>
       <c r="I461" t="n">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="462">
@@ -19171,7 +19171,7 @@
         <v>76</v>
       </c>
       <c r="I462" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="463">
@@ -19212,7 +19212,7 @@
         <v>26</v>
       </c>
       <c r="I463" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="464">
@@ -19245,7 +19245,7 @@
         <v>24</v>
       </c>
       <c r="I464" t="n">
-        <v>3.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="465">
@@ -19286,7 +19286,7 @@
         <v>51</v>
       </c>
       <c r="I465" t="n">
-        <v>2</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="466">
@@ -19366,7 +19366,7 @@
         <v>9</v>
       </c>
       <c r="I467" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="468">
@@ -19448,7 +19448,7 @@
         <v>15</v>
       </c>
       <c r="I469" t="n">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="470">
@@ -19530,7 +19530,7 @@
         <v>29</v>
       </c>
       <c r="I471" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="472">
@@ -19612,7 +19612,7 @@
         <v>61</v>
       </c>
       <c r="I473" t="n">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="474">
@@ -19653,7 +19653,7 @@
         <v>61</v>
       </c>
       <c r="I474" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="475">
@@ -19690,7 +19690,7 @@
         <v>53</v>
       </c>
       <c r="I475" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="476">
@@ -19885,7 +19885,7 @@
         <v>74</v>
       </c>
       <c r="I480" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="481">
@@ -19918,7 +19918,7 @@
         <v>42</v>
       </c>
       <c r="I481" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="482">
@@ -19958,9 +19958,7 @@
       <c r="H482" t="n">
         <v>61</v>
       </c>
-      <c r="I482" t="n">
-        <v>1.4</v>
-      </c>
+      <c r="I482" t="inlineStr"/>
     </row>
     <row r="483">
       <c r="A483" t="n">
@@ -20000,7 +19998,7 @@
         <v>61</v>
       </c>
       <c r="I483" t="n">
-        <v>1.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="484">
@@ -20041,7 +20039,7 @@
         <v>22</v>
       </c>
       <c r="I484" t="n">
-        <v>4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="485">
@@ -20121,7 +20119,7 @@
         <v>18</v>
       </c>
       <c r="I486" t="n">
-        <v>4.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="487">
@@ -20162,7 +20160,7 @@
         <v>42</v>
       </c>
       <c r="I487" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="488">
@@ -20242,7 +20240,7 @@
         <v>36</v>
       </c>
       <c r="I489" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="490">
@@ -20283,7 +20281,7 @@
         <v>7</v>
       </c>
       <c r="I490" t="n">
-        <v>6.9</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="491">
@@ -20324,7 +20322,7 @@
         <v>33</v>
       </c>
       <c r="I491" t="n">
-        <v>2.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="492">
@@ -20365,7 +20363,7 @@
         <v>2</v>
       </c>
       <c r="I492" t="n">
-        <v>2.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="493">
@@ -20406,7 +20404,7 @@
         <v>1</v>
       </c>
       <c r="I493" t="n">
-        <v>10.6</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="494">
@@ -20447,7 +20445,7 @@
         <v>9</v>
       </c>
       <c r="I494" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="495">
@@ -20488,7 +20486,7 @@
         <v>12</v>
       </c>
       <c r="I495" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
@@ -20570,7 +20568,7 @@
         <v>13</v>
       </c>
       <c r="I497" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="498">
@@ -20611,7 +20609,7 @@
         <v>4</v>
       </c>
       <c r="I498" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="499">
@@ -20652,7 +20650,7 @@
         <v>13</v>
       </c>
       <c r="I499" t="n">
-        <v>1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="500">
@@ -20693,7 +20691,7 @@
         <v>17</v>
       </c>
       <c r="I500" t="n">
-        <v>0.9</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="501">
@@ -20734,7 +20732,7 @@
         <v>9</v>
       </c>
       <c r="I501" t="n">
-        <v>1.3</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="502">
@@ -20774,9 +20772,7 @@
       <c r="H502" t="n">
         <v>9</v>
       </c>
-      <c r="I502" t="n">
-        <v>1.3</v>
-      </c>
+      <c r="I502" t="inlineStr"/>
     </row>
     <row r="503">
       <c r="A503" t="n">
@@ -20898,7 +20894,7 @@
         <v>21</v>
       </c>
       <c r="I505" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="506">
@@ -20980,7 +20976,7 @@
         <v>17</v>
       </c>
       <c r="I507" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="508">
@@ -21021,7 +21017,7 @@
         <v>3</v>
       </c>
       <c r="I508" t="n">
-        <v>1.8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -21062,7 +21058,7 @@
         <v>4</v>
       </c>
       <c r="I509" t="n">
-        <v>1.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="510">
@@ -21103,7 +21099,7 @@
         <v>13</v>
       </c>
       <c r="I510" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="511">
@@ -21144,7 +21140,7 @@
         <v>21</v>
       </c>
       <c r="I511" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="512">
@@ -21185,7 +21181,7 @@
         <v>21</v>
       </c>
       <c r="I512" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="513">
@@ -21226,7 +21222,7 @@
         <v>26</v>
       </c>
       <c r="I513" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
     </row>
     <row r="514">
@@ -21267,7 +21263,7 @@
         <v>6</v>
       </c>
       <c r="I514" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="515">
@@ -21343,7 +21339,7 @@
         <v>25</v>
       </c>
       <c r="I516" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="517">
@@ -21380,7 +21376,7 @@
         <v>8</v>
       </c>
       <c r="I517" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="518">
@@ -21421,7 +21417,7 @@
         <v>13</v>
       </c>
       <c r="I518" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="519">
@@ -21462,7 +21458,7 @@
         <v>3</v>
       </c>
       <c r="I519" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="520">
@@ -21503,7 +21499,7 @@
         <v>3</v>
       </c>
       <c r="I520" t="n">
-        <v>8</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="521">
@@ -21544,7 +21540,7 @@
         <v>20</v>
       </c>
       <c r="I521" t="n">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="522">
@@ -21585,7 +21581,7 @@
         <v>8</v>
       </c>
       <c r="I522" t="n">
-        <v>4.3</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="523">
@@ -21626,7 +21622,7 @@
         <v>5</v>
       </c>
       <c r="I523" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="524">
@@ -21667,7 +21663,7 @@
         <v>13</v>
       </c>
       <c r="I524" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="525">
@@ -21708,7 +21704,7 @@
         <v>2</v>
       </c>
       <c r="I525" t="n">
-        <v>10.9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="526">
@@ -21749,7 +21745,7 @@
         <v>9</v>
       </c>
       <c r="I526" t="n">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="527">
@@ -21790,7 +21786,7 @@
         <v>16</v>
       </c>
       <c r="I527" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="528">
@@ -21831,7 +21827,7 @@
         <v>5</v>
       </c>
       <c r="I528" t="n">
-        <v>5.7</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="529">
@@ -21909,7 +21905,7 @@
         <v>12</v>
       </c>
       <c r="I530" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="531">
@@ -21950,7 +21946,7 @@
         <v>9</v>
       </c>
       <c r="I531" t="n">
-        <v>4.2</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="532">
@@ -21991,7 +21987,7 @@
         <v>20</v>
       </c>
       <c r="I532" t="n">
-        <v>1.8</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="533">
@@ -22032,7 +22028,7 @@
         <v>23</v>
       </c>
       <c r="I533" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="534">
@@ -22073,7 +22069,7 @@
         <v>11</v>
       </c>
       <c r="I534" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="535">
@@ -22114,7 +22110,7 @@
         <v>17</v>
       </c>
       <c r="I535" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="536">
@@ -22155,7 +22151,7 @@
         <v>14</v>
       </c>
       <c r="I536" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="537">
@@ -22196,7 +22192,7 @@
         <v>18</v>
       </c>
       <c r="I537" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="538">
@@ -22237,7 +22233,7 @@
         <v>19</v>
       </c>
       <c r="I538" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="539">
@@ -22278,7 +22274,7 @@
         <v>1</v>
       </c>
       <c r="I539" t="n">
-        <v>13.3</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="540">
@@ -22319,7 +22315,7 @@
         <v>15</v>
       </c>
       <c r="I540" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="541">
@@ -22399,7 +22395,7 @@
         <v>24</v>
       </c>
       <c r="I542" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="543">
@@ -22440,7 +22436,7 @@
         <v>25</v>
       </c>
       <c r="I543" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="544">
@@ -22481,7 +22477,7 @@
         <v>7</v>
       </c>
       <c r="I544" t="n">
-        <v>5.3</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="545">
@@ -22561,7 +22557,7 @@
         <v>2</v>
       </c>
       <c r="I546" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="547">
@@ -22602,7 +22598,7 @@
         <v>4</v>
       </c>
       <c r="I547" t="n">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="548">
@@ -22643,7 +22639,7 @@
         <v>7</v>
       </c>
       <c r="I548" t="n">
-        <v>2.4</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="549">
@@ -22725,7 +22721,7 @@
         <v>1</v>
       </c>
       <c r="I550" t="n">
-        <v>6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="551">
@@ -22766,7 +22762,7 @@
         <v>5</v>
       </c>
       <c r="I551" t="n">
-        <v>3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="552">
@@ -22807,7 +22803,7 @@
         <v>15</v>
       </c>
       <c r="I552" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="553">
@@ -22848,7 +22844,7 @@
         <v>6</v>
       </c>
       <c r="I553" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="554">
@@ -22889,7 +22885,7 @@
         <v>3</v>
       </c>
       <c r="I554" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="555">
@@ -22930,7 +22926,7 @@
         <v>10</v>
       </c>
       <c r="I555" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="556">
@@ -22971,7 +22967,7 @@
         <v>12</v>
       </c>
       <c r="I556" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557">
@@ -23053,7 +23049,7 @@
         <v>9</v>
       </c>
       <c r="I558" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="559">
@@ -23094,7 +23090,7 @@
         <v>17</v>
       </c>
       <c r="I559" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="560">
@@ -23135,7 +23131,7 @@
         <v>13</v>
       </c>
       <c r="I560" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="561">
@@ -23176,7 +23172,7 @@
         <v>13</v>
       </c>
       <c r="I561" t="n">
-        <v>1.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="562">
@@ -23256,7 +23252,7 @@
         <v>5</v>
       </c>
       <c r="I563" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="564">
@@ -23297,7 +23293,7 @@
         <v>13</v>
       </c>
       <c r="I564" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="565">
@@ -23338,7 +23334,7 @@
         <v>11</v>
       </c>
       <c r="I565" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="566">
@@ -23420,7 +23416,7 @@
         <v>12</v>
       </c>
       <c r="I567" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="568">
@@ -23502,7 +23498,7 @@
         <v>8</v>
       </c>
       <c r="I569" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="570">
@@ -23543,7 +23539,7 @@
         <v>2</v>
       </c>
       <c r="I570" t="n">
-        <v>2.3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="571">
@@ -23707,7 +23703,7 @@
         <v>7</v>
       </c>
       <c r="I574" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="575">
@@ -23789,7 +23785,7 @@
         <v>24</v>
       </c>
       <c r="I576" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="577">
@@ -23830,7 +23826,7 @@
         <v>8</v>
       </c>
       <c r="I577" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="578">
@@ -23871,7 +23867,7 @@
         <v>2</v>
       </c>
       <c r="I578" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="579">
@@ -23992,7 +23988,7 @@
         <v>21</v>
       </c>
       <c r="I581" t="n">
-        <v>0.5</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="582">
@@ -24033,7 +24029,7 @@
         <v>20</v>
       </c>
       <c r="I582" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
     </row>
     <row r="583">
@@ -24074,7 +24070,7 @@
         <v>4</v>
       </c>
       <c r="I583" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="584">
@@ -24193,7 +24189,7 @@
         <v>1</v>
       </c>
       <c r="I586" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="587">
@@ -24234,7 +24230,7 @@
         <v>13</v>
       </c>
       <c r="I587" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="588">
@@ -24275,7 +24271,7 @@
         <v>11</v>
       </c>
       <c r="I588" t="n">
-        <v>7</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="589">
@@ -24316,7 +24312,7 @@
         <v>1</v>
       </c>
       <c r="I589" t="n">
-        <v>12.4</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="590">
@@ -24357,7 +24353,7 @@
         <v>7</v>
       </c>
       <c r="I590" t="n">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="591">
@@ -24398,7 +24394,7 @@
         <v>24</v>
       </c>
       <c r="I591" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="592">
@@ -24439,7 +24435,7 @@
         <v>18</v>
       </c>
       <c r="I592" t="n">
-        <v>4.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="593">
@@ -24480,7 +24476,7 @@
         <v>20</v>
       </c>
       <c r="I593" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="594">
@@ -24521,7 +24517,7 @@
         <v>3</v>
       </c>
       <c r="I594" t="n">
-        <v>9</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="595">
@@ -24603,7 +24599,7 @@
         <v>15</v>
       </c>
       <c r="I596" t="n">
-        <v>5.3</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="597">
@@ -24644,7 +24640,7 @@
         <v>31</v>
       </c>
       <c r="I597" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="598">
@@ -24685,7 +24681,7 @@
         <v>7</v>
       </c>
       <c r="I598" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="599">
@@ -24726,7 +24722,7 @@
         <v>22</v>
       </c>
       <c r="I599" t="n">
-        <v>3.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="600">
@@ -24767,7 +24763,7 @@
         <v>33</v>
       </c>
       <c r="I600" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="601">
@@ -24808,7 +24804,7 @@
         <v>14</v>
       </c>
       <c r="I601" t="n">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="602">
@@ -24849,7 +24845,7 @@
         <v>10</v>
       </c>
       <c r="I602" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="603">
@@ -24890,7 +24886,7 @@
         <v>7</v>
       </c>
       <c r="I603" t="n">
-        <v>7.8</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="604">
@@ -24931,7 +24927,7 @@
         <v>2</v>
       </c>
       <c r="I604" t="n">
-        <v>11</v>
+        <v>12.4</v>
       </c>
     </row>
     <row r="605">
@@ -24972,7 +24968,7 @@
         <v>21</v>
       </c>
       <c r="I605" t="n">
-        <v>3.5</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="606">
@@ -25005,7 +25001,7 @@
         <v>33</v>
       </c>
       <c r="I606" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="607">
@@ -25046,7 +25042,7 @@
         <v>3</v>
       </c>
       <c r="I607" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="608">
@@ -25087,7 +25083,7 @@
         <v>16</v>
       </c>
       <c r="I608" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="609">
@@ -25169,7 +25165,7 @@
         <v>28</v>
       </c>
       <c r="I610" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="611">
@@ -25210,7 +25206,7 @@
         <v>19</v>
       </c>
       <c r="I611" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="612">
@@ -25251,7 +25247,7 @@
         <v>36</v>
       </c>
       <c r="I612" t="n">
-        <v>1.1</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="613">
@@ -25292,7 +25288,7 @@
         <v>23</v>
       </c>
       <c r="I613" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="614">
@@ -25333,7 +25329,7 @@
         <v>17</v>
       </c>
       <c r="I614" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="615">
@@ -25374,7 +25370,7 @@
         <v>12</v>
       </c>
       <c r="I615" t="n">
-        <v>6.9</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="616">
@@ -25415,7 +25411,7 @@
         <v>26</v>
       </c>
       <c r="I616" t="n">
-        <v>2.6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="617">
@@ -25456,7 +25452,7 @@
         <v>37</v>
       </c>
       <c r="I617" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="618">
@@ -25497,7 +25493,7 @@
         <v>25</v>
       </c>
       <c r="I618" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="619">
@@ -25538,7 +25534,7 @@
         <v>30</v>
       </c>
       <c r="I619" t="n">
-        <v>2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="620">
@@ -25579,7 +25575,7 @@
         <v>12</v>
       </c>
       <c r="I620" t="n">
-        <v>6.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="621">
@@ -25620,7 +25616,7 @@
         <v>29</v>
       </c>
       <c r="I621" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="622">
@@ -25661,7 +25657,7 @@
         <v>27</v>
       </c>
       <c r="I622" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="623">
@@ -25702,7 +25698,7 @@
         <v>35</v>
       </c>
       <c r="I623" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="624">
@@ -25743,7 +25739,7 @@
         <v>6</v>
       </c>
       <c r="I624" t="n">
-        <v>7.9</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="625">
@@ -25784,7 +25780,7 @@
         <v>8</v>
       </c>
       <c r="I625" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="626">
@@ -25825,7 +25821,7 @@
         <v>4</v>
       </c>
       <c r="I626" t="n">
-        <v>4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="627">
@@ -25866,7 +25862,7 @@
         <v>6</v>
       </c>
       <c r="I627" t="n">
-        <v>3.5</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="628">
@@ -25907,7 +25903,7 @@
         <v>1</v>
       </c>
       <c r="I628" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="629">
@@ -25948,7 +25944,7 @@
         <v>3</v>
       </c>
       <c r="I629" t="n">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="630">
@@ -25989,7 +25985,7 @@
         <v>7</v>
       </c>
       <c r="I630" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="631">
@@ -26030,7 +26026,7 @@
         <v>9</v>
       </c>
       <c r="I631" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="632">
@@ -26071,7 +26067,7 @@
         <v>9</v>
       </c>
       <c r="I632" t="n">
-        <v>3.3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="633">
@@ -26112,7 +26108,7 @@
         <v>2</v>
       </c>
       <c r="I633" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="634">
@@ -26153,7 +26149,7 @@
         <v>13</v>
       </c>
       <c r="I634" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="635">
@@ -26194,7 +26190,7 @@
         <v>5</v>
       </c>
       <c r="I635" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="636">
@@ -26235,7 +26231,7 @@
         <v>12</v>
       </c>
       <c r="I636" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="637">
@@ -26276,7 +26272,7 @@
         <v>11</v>
       </c>
       <c r="I637" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="638">
@@ -26317,7 +26313,7 @@
         <v>13</v>
       </c>
       <c r="I638" t="n">
-        <v>1.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="639">
@@ -26358,7 +26354,7 @@
         <v>1</v>
       </c>
       <c r="I639" t="n">
-        <v>8.9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="640">
@@ -26399,7 +26395,7 @@
         <v>5</v>
       </c>
       <c r="I640" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="641">
@@ -26440,7 +26436,7 @@
         <v>12</v>
       </c>
       <c r="I641" t="n">
-        <v>2.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="642">
@@ -26520,7 +26516,7 @@
         <v>9</v>
       </c>
       <c r="I643" t="n">
-        <v>2.9</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="644">
@@ -26561,7 +26557,7 @@
         <v>11</v>
       </c>
       <c r="I644" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="645">
@@ -26643,7 +26639,7 @@
         <v>19</v>
       </c>
       <c r="I646" t="n">
-        <v>1.9</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="647">
@@ -26684,7 +26680,7 @@
         <v>13</v>
       </c>
       <c r="I647" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="648">
@@ -26725,7 +26721,7 @@
         <v>9</v>
       </c>
       <c r="I648" t="n">
-        <v>2.9</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="649">
@@ -26766,7 +26762,7 @@
         <v>7</v>
       </c>
       <c r="I649" t="n">
-        <v>4.2</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="650">
@@ -26807,7 +26803,7 @@
         <v>8</v>
       </c>
       <c r="I650" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="651">
@@ -26848,7 +26844,7 @@
         <v>16</v>
       </c>
       <c r="I651" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="652">
@@ -26889,7 +26885,7 @@
         <v>6</v>
       </c>
       <c r="I652" t="n">
-        <v>4.7</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="653">
@@ -26930,7 +26926,7 @@
         <v>23</v>
       </c>
       <c r="I653" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="654">
@@ -26971,7 +26967,7 @@
         <v>23</v>
       </c>
       <c r="I654" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="655">
@@ -27012,7 +27008,7 @@
         <v>16</v>
       </c>
       <c r="I655" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="656">
@@ -27053,7 +27049,7 @@
         <v>19</v>
       </c>
       <c r="I656" t="n">
-        <v>1.9</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="657">
@@ -27094,7 +27090,7 @@
         <v>16</v>
       </c>
       <c r="I657" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="658">
@@ -27135,7 +27131,7 @@
         <v>21</v>
       </c>
       <c r="I658" t="n">
-        <v>1.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="659">
@@ -27176,7 +27172,7 @@
         <v>21</v>
       </c>
       <c r="I659" t="n">
-        <v>1.8</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="660">
@@ -27217,7 +27213,7 @@
         <v>2</v>
       </c>
       <c r="I660" t="n">
-        <v>6.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="661">
@@ -27258,7 +27254,7 @@
         <v>14</v>
       </c>
       <c r="I661" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="662">
@@ -27291,7 +27287,7 @@
         <v>4</v>
       </c>
       <c r="I662" t="n">
-        <v>5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="663">
@@ -27332,7 +27328,7 @@
         <v>2</v>
       </c>
       <c r="I663" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="664">
@@ -27373,7 +27369,7 @@
         <v>5</v>
       </c>
       <c r="I664" t="n">
-        <v>6.2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="665">
@@ -27414,7 +27410,7 @@
         <v>20</v>
       </c>
       <c r="I665" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="666">
@@ -27455,7 +27451,7 @@
         <v>26</v>
       </c>
       <c r="I666" t="n">
-        <v>2.2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="667">
@@ -27496,7 +27492,7 @@
         <v>19</v>
       </c>
       <c r="I667" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="668">
@@ -27537,7 +27533,7 @@
         <v>16</v>
       </c>
       <c r="I668" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="669">
@@ -27578,7 +27574,7 @@
         <v>1</v>
       </c>
       <c r="I669" t="n">
-        <v>13</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="670">
@@ -27619,7 +27615,7 @@
         <v>13</v>
       </c>
       <c r="I670" t="n">
-        <v>3.7</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="671">
@@ -27660,7 +27656,7 @@
         <v>28</v>
       </c>
       <c r="I671" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="672">
@@ -27701,7 +27697,7 @@
         <v>29</v>
       </c>
       <c r="I672" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="673">
@@ -27742,7 +27738,7 @@
         <v>6</v>
       </c>
       <c r="I673" t="n">
-        <v>5.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="674">
@@ -27783,7 +27779,7 @@
         <v>4</v>
       </c>
       <c r="I674" t="n">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="675">
@@ -27824,7 +27820,7 @@
         <v>3</v>
       </c>
       <c r="I675" t="n">
-        <v>7.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="676">
@@ -27865,7 +27861,7 @@
         <v>13</v>
       </c>
       <c r="I676" t="n">
-        <v>3.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="677">
@@ -27906,7 +27902,7 @@
         <v>12</v>
       </c>
       <c r="I677" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="678">
@@ -27947,7 +27943,7 @@
         <v>8</v>
       </c>
       <c r="I678" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="679">
@@ -27988,7 +27984,7 @@
         <v>9</v>
       </c>
       <c r="I679" t="n">
-        <v>4.2</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="680">
@@ -28029,7 +28025,7 @@
         <v>25</v>
       </c>
       <c r="I680" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="681">
@@ -28111,7 +28107,7 @@
         <v>27</v>
       </c>
       <c r="I682" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="683">
@@ -28152,7 +28148,7 @@
         <v>11</v>
       </c>
       <c r="I683" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="684">
@@ -28193,7 +28189,7 @@
         <v>7</v>
       </c>
       <c r="I684" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="685">
@@ -28234,7 +28230,7 @@
         <v>15</v>
       </c>
       <c r="I685" t="n">
-        <v>3.5</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="686">
@@ -28271,7 +28267,7 @@
         <v>24</v>
       </c>
       <c r="I686" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="687">
@@ -28312,7 +28308,7 @@
         <v>20</v>
       </c>
       <c r="I687" t="n">
-        <v>2.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="688">
@@ -28353,7 +28349,7 @@
         <v>20</v>
       </c>
       <c r="I688" t="n">
-        <v>2.6</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="689">
@@ -28433,7 +28429,7 @@
         <v>9</v>
       </c>
       <c r="I690" t="n">
-        <v>4.2</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="691">
@@ -28470,7 +28466,7 @@
         <v>20</v>
       </c>
       <c r="I691" t="n">
-        <v>2.6</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="692">
@@ -28511,7 +28507,7 @@
         <v>30</v>
       </c>
       <c r="I692" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="693">
@@ -28552,7 +28548,7 @@
         <v>18</v>
       </c>
       <c r="I693" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="694">
@@ -28593,7 +28589,7 @@
         <v>2</v>
       </c>
       <c r="I694" t="n">
-        <v>4.3</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="695">
@@ -28634,7 +28630,7 @@
         <v>1</v>
       </c>
       <c r="I695" t="n">
-        <v>6.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="696">
@@ -28675,7 +28671,7 @@
         <v>11</v>
       </c>
       <c r="I696" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="697">
@@ -28716,7 +28712,7 @@
         <v>13</v>
       </c>
       <c r="I697" t="n">
-        <v>1.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="698">
@@ -28757,7 +28753,7 @@
         <v>3</v>
       </c>
       <c r="I698" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="699">
@@ -28798,7 +28794,7 @@
         <v>7</v>
       </c>
       <c r="I699" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="700">
@@ -28839,7 +28835,7 @@
         <v>8</v>
       </c>
       <c r="I700" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="701">
@@ -28880,7 +28876,7 @@
         <v>3</v>
       </c>
       <c r="I701" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="702">
@@ -28921,7 +28917,7 @@
         <v>8</v>
       </c>
       <c r="I702" t="n">
-        <v>2.3</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="703">
@@ -29003,7 +28999,7 @@
         <v>14</v>
       </c>
       <c r="I704" t="n">
-        <v>1.5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="705">
@@ -29044,7 +29040,7 @@
         <v>3</v>
       </c>
       <c r="I705" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="706">
@@ -29085,7 +29081,7 @@
         <v>3</v>
       </c>
       <c r="I706" t="n">
-        <v>3.5</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="707">
@@ -29167,7 +29163,7 @@
         <v>14</v>
       </c>
       <c r="I708" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="709">
@@ -29208,7 +29204,7 @@
         <v>12</v>
       </c>
       <c r="I709" t="n">
-        <v>1.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="710">
@@ -29249,7 +29245,7 @@
         <v>10</v>
       </c>
       <c r="I710" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="711">
@@ -29290,7 +29286,7 @@
         <v>23</v>
       </c>
       <c r="I711" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="712">
@@ -29331,7 +29327,7 @@
         <v>9</v>
       </c>
       <c r="I712" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="713">
@@ -29372,7 +29368,7 @@
         <v>26</v>
       </c>
       <c r="I713" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="714">
@@ -29413,7 +29409,7 @@
         <v>1</v>
       </c>
       <c r="I714" t="n">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="715">
@@ -29454,7 +29450,7 @@
         <v>13</v>
       </c>
       <c r="I715" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="716">
@@ -29495,7 +29491,7 @@
         <v>25</v>
       </c>
       <c r="I716" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="717">
@@ -29536,7 +29532,7 @@
         <v>3</v>
       </c>
       <c r="I717" t="n">
-        <v>5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="718">
@@ -29577,7 +29573,7 @@
         <v>20</v>
       </c>
       <c r="I718" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="719">
@@ -29618,7 +29614,7 @@
         <v>16</v>
       </c>
       <c r="I719" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="720">
@@ -29659,7 +29655,7 @@
         <v>17</v>
       </c>
       <c r="I720" t="n">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="721">
@@ -29700,7 +29696,7 @@
         <v>26</v>
       </c>
       <c r="I721" t="n">
-        <v>2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="722">
@@ -29741,7 +29737,7 @@
         <v>10</v>
       </c>
       <c r="I722" t="n">
-        <v>3.4</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="723">
@@ -29782,7 +29778,7 @@
         <v>28</v>
       </c>
       <c r="I723" t="n">
-        <v>1.7</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="724">
@@ -29823,7 +29819,7 @@
         <v>7</v>
       </c>
       <c r="I724" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="725">
@@ -29864,7 +29860,7 @@
         <v>14</v>
       </c>
       <c r="I725" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="726">
@@ -29905,7 +29901,7 @@
         <v>17</v>
       </c>
       <c r="I726" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="727">
@@ -29946,7 +29942,7 @@
         <v>20</v>
       </c>
       <c r="I727" t="n">
-        <v>2.7</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="728">
@@ -29987,7 +29983,7 @@
         <v>4</v>
       </c>
       <c r="I728" t="n">
-        <v>4.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="729">
@@ -30028,7 +30024,7 @@
         <v>17</v>
       </c>
       <c r="I729" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="730">
@@ -30069,7 +30065,7 @@
         <v>7</v>
       </c>
       <c r="I730" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="731">
@@ -30110,7 +30106,7 @@
         <v>14</v>
       </c>
       <c r="I731" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="732">
@@ -30151,7 +30147,7 @@
         <v>4</v>
       </c>
       <c r="I732" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="733">
@@ -30192,7 +30188,7 @@
         <v>20</v>
       </c>
       <c r="I733" t="n">
-        <v>2.7</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="734">
@@ -30233,7 +30229,7 @@
         <v>6</v>
       </c>
       <c r="I734" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="735">
@@ -30274,7 +30270,7 @@
         <v>11</v>
       </c>
       <c r="I735" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="736">
@@ -30315,7 +30311,7 @@
         <v>2</v>
       </c>
       <c r="I736" t="n">
-        <v>6.5</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="737">
@@ -30356,7 +30352,7 @@
         <v>11</v>
       </c>
       <c r="I737" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="738">
@@ -30397,7 +30393,7 @@
         <v>23</v>
       </c>
       <c r="I738" t="n">
-        <v>2.4</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="739">
@@ -30479,7 +30475,7 @@
         <v>5</v>
       </c>
       <c r="I740" t="n">
-        <v>6.1</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="741">
@@ -30520,7 +30516,7 @@
         <v>13</v>
       </c>
       <c r="I741" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="742">
@@ -30561,7 +30557,7 @@
         <v>4</v>
       </c>
       <c r="I742" t="n">
-        <v>6.4</v>
+        <v>10.8</v>
       </c>
     </row>
     <row r="743">
@@ -30602,7 +30598,7 @@
         <v>9</v>
       </c>
       <c r="I743" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="744">
@@ -30643,7 +30639,7 @@
         <v>1</v>
       </c>
       <c r="I744" t="n">
-        <v>29.4</v>
+        <v>41.8</v>
       </c>
     </row>
     <row r="745">
@@ -30723,7 +30719,7 @@
         <v>15</v>
       </c>
       <c r="I746" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="747">
@@ -30764,7 +30760,7 @@
         <v>19</v>
       </c>
       <c r="I747" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="748">
@@ -30805,7 +30801,7 @@
         <v>7</v>
       </c>
       <c r="I748" t="n">
-        <v>5.8</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="749">
@@ -30887,7 +30883,7 @@
         <v>10</v>
       </c>
       <c r="I750" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="751">
@@ -30928,7 +30924,7 @@
         <v>35</v>
       </c>
       <c r="I751" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="752">
@@ -30969,7 +30965,7 @@
         <v>17</v>
       </c>
       <c r="I752" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="753">
@@ -31010,7 +31006,7 @@
         <v>14</v>
       </c>
       <c r="I753" t="n">
-        <v>3.5</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="754">
@@ -31051,7 +31047,7 @@
         <v>12</v>
       </c>
       <c r="I754" t="n">
-        <v>3.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="755">
@@ -31092,7 +31088,7 @@
         <v>3</v>
       </c>
       <c r="I755" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="756">
@@ -31133,7 +31129,7 @@
         <v>8</v>
       </c>
       <c r="I756" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="757">
@@ -31174,7 +31170,7 @@
         <v>22</v>
       </c>
       <c r="I757" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="758">
@@ -31215,7 +31211,7 @@
         <v>2</v>
       </c>
       <c r="I758" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
     </row>
     <row r="759">
@@ -31256,7 +31252,7 @@
         <v>19</v>
       </c>
       <c r="I759" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="760">
@@ -31297,7 +31293,7 @@
         <v>6</v>
       </c>
       <c r="I760" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="761">
@@ -31338,7 +31334,7 @@
         <v>26</v>
       </c>
       <c r="I761" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="762">
@@ -31379,7 +31375,7 @@
         <v>19</v>
       </c>
       <c r="I762" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="763">
@@ -31420,7 +31416,7 @@
         <v>31</v>
       </c>
       <c r="I763" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="764">
@@ -31461,7 +31457,7 @@
         <v>33</v>
       </c>
       <c r="I764" t="n">
-        <v>2.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="765">
@@ -31502,7 +31498,7 @@
         <v>33</v>
       </c>
       <c r="I765" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="766">
@@ -31543,7 +31539,7 @@
         <v>23</v>
       </c>
       <c r="I766" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="767">
@@ -31584,7 +31580,7 @@
         <v>23</v>
       </c>
       <c r="I767" t="n">
-        <v>2.8</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="768">
@@ -31625,7 +31621,7 @@
         <v>23</v>
       </c>
       <c r="I768" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="769">
@@ -31666,7 +31662,7 @@
         <v>26</v>
       </c>
       <c r="I769" t="n">
-        <v>2.7</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="770">
@@ -31707,7 +31703,7 @@
         <v>30</v>
       </c>
       <c r="I770" t="n">
-        <v>2.6</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="771">
@@ -31748,7 +31744,7 @@
         <v>32</v>
       </c>
       <c r="I771" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="772">
@@ -31789,7 +31785,7 @@
         <v>17</v>
       </c>
       <c r="I772" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="773">
@@ -31830,7 +31826,7 @@
         <v>38</v>
       </c>
       <c r="I773" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="774">
@@ -31912,7 +31908,7 @@
         <v>26</v>
       </c>
       <c r="I775" t="n">
-        <v>2.7</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="776">
@@ -31953,7 +31949,7 @@
         <v>37</v>
       </c>
       <c r="I776" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="777">
@@ -31994,7 +31990,7 @@
         <v>15</v>
       </c>
       <c r="I777" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="778">
@@ -32035,7 +32031,7 @@
         <v>34</v>
       </c>
       <c r="I778" t="n">
-        <v>5.1</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="779">
@@ -32076,7 +32072,7 @@
         <v>26</v>
       </c>
       <c r="I779" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="780">
@@ -32117,7 +32113,7 @@
         <v>31</v>
       </c>
       <c r="I780" t="n">
-        <v>5.5</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="781">
@@ -32158,7 +32154,7 @@
         <v>27</v>
       </c>
       <c r="I781" t="n">
-        <v>6</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="782">
@@ -32199,7 +32195,7 @@
         <v>21</v>
       </c>
       <c r="I782" t="n">
-        <v>6.6</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="783">
@@ -32240,7 +32236,7 @@
         <v>9</v>
       </c>
       <c r="I783" t="n">
-        <v>9.1</v>
+        <v>11.2</v>
       </c>
     </row>
     <row r="784">
@@ -32281,7 +32277,7 @@
         <v>36</v>
       </c>
       <c r="I784" t="n">
-        <v>4.8</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="785">
@@ -32322,7 +32318,7 @@
         <v>50</v>
       </c>
       <c r="I785" t="n">
-        <v>3.6</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="786">
@@ -32363,7 +32359,7 @@
         <v>4</v>
       </c>
       <c r="I786" t="n">
-        <v>12.2</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="787">
@@ -32404,7 +32400,7 @@
         <v>11</v>
       </c>
       <c r="I787" t="n">
-        <v>8.9</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="788">
@@ -32445,7 +32441,7 @@
         <v>60</v>
       </c>
       <c r="I788" t="n">
-        <v>2.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="789">
@@ -32486,7 +32482,7 @@
         <v>69</v>
       </c>
       <c r="I789" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="790">
@@ -32527,7 +32523,7 @@
         <v>17</v>
       </c>
       <c r="I790" t="n">
-        <v>6.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="791">
@@ -32568,7 +32564,7 @@
         <v>12</v>
       </c>
       <c r="I791" t="n">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="792">
@@ -32609,7 +32605,7 @@
         <v>6</v>
       </c>
       <c r="I792" t="n">
-        <v>10.4</v>
+        <v>11.6</v>
       </c>
     </row>
     <row r="793">
@@ -32650,7 +32646,7 @@
         <v>29</v>
       </c>
       <c r="I793" t="n">
-        <v>5.6</v>
+        <v>6</v>
       </c>
     </row>
     <row r="794">
@@ -32691,7 +32687,7 @@
         <v>14</v>
       </c>
       <c r="I794" t="n">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
     </row>
     <row r="795">
@@ -32732,7 +32728,7 @@
         <v>37</v>
       </c>
       <c r="I795" t="n">
-        <v>4.7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="796">
@@ -32773,7 +32769,7 @@
         <v>41</v>
       </c>
       <c r="I796" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="797">
@@ -32814,7 +32810,7 @@
         <v>17</v>
       </c>
       <c r="I797" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="798">
@@ -32855,7 +32851,7 @@
         <v>57</v>
       </c>
       <c r="I798" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="799">
@@ -32896,7 +32892,7 @@
         <v>13</v>
       </c>
       <c r="I799" t="n">
-        <v>8.300000000000001</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="800">
@@ -32937,7 +32933,7 @@
         <v>24</v>
       </c>
       <c r="I800" t="n">
-        <v>6.3</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="801">
@@ -32978,7 +32974,7 @@
         <v>29</v>
       </c>
       <c r="I801" t="n">
-        <v>5.6</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="802">
@@ -33019,7 +33015,7 @@
         <v>48</v>
       </c>
       <c r="I802" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="803">
@@ -33060,7 +33056,7 @@
         <v>2</v>
       </c>
       <c r="I803" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
     </row>
     <row r="804">
@@ -33101,7 +33097,7 @@
         <v>17</v>
       </c>
       <c r="I804" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="805">
@@ -33142,7 +33138,7 @@
         <v>32</v>
       </c>
       <c r="I805" t="n">
-        <v>5.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="806">
@@ -33224,7 +33220,7 @@
         <v>5</v>
       </c>
       <c r="I807" t="n">
-        <v>11.8</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="808">
@@ -33265,7 +33261,7 @@
         <v>58</v>
       </c>
       <c r="I808" t="n">
-        <v>2.9</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="809">
@@ -33306,7 +33302,7 @@
         <v>1</v>
       </c>
       <c r="I809" t="n">
-        <v>28</v>
+        <v>30.4</v>
       </c>
     </row>
     <row r="810">
@@ -33384,7 +33380,7 @@
         <v>56</v>
       </c>
       <c r="I811" t="n">
-        <v>3.1</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="812">
@@ -33425,7 +33421,7 @@
         <v>6</v>
       </c>
       <c r="I812" t="n">
-        <v>10.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="813">
@@ -33466,7 +33462,7 @@
         <v>64</v>
       </c>
       <c r="I813" t="n">
-        <v>2.2</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="814">
@@ -33546,7 +33542,7 @@
         <v>32</v>
       </c>
       <c r="I815" t="n">
-        <v>5.4</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="816">
@@ -33587,7 +33583,7 @@
         <v>9</v>
       </c>
       <c r="I816" t="n">
-        <v>9.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="817">
@@ -33628,7 +33624,7 @@
         <v>37</v>
       </c>
       <c r="I817" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="818">
@@ -33669,7 +33665,7 @@
         <v>24</v>
       </c>
       <c r="I818" t="n">
-        <v>6.3</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="819">
@@ -33710,7 +33706,7 @@
         <v>17</v>
       </c>
       <c r="I819" t="n">
-        <v>6.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="820">
@@ -33747,7 +33743,7 @@
         <v>45</v>
       </c>
       <c r="I820" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="821">
@@ -33784,7 +33780,7 @@
         <v>62</v>
       </c>
       <c r="I821" t="n">
-        <v>2.3</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="822">
@@ -33825,7 +33821,7 @@
         <v>16</v>
       </c>
       <c r="I822" t="n">
-        <v>7.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="823">
@@ -33866,7 +33862,7 @@
         <v>40</v>
       </c>
       <c r="I823" t="n">
-        <v>4.4</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="824">
@@ -33907,7 +33903,7 @@
         <v>37</v>
       </c>
       <c r="I824" t="n">
-        <v>4.7</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="825">
@@ -33948,7 +33944,7 @@
         <v>55</v>
       </c>
       <c r="I825" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="826">
@@ -33989,7 +33985,7 @@
         <v>52</v>
       </c>
       <c r="I826" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="827">
@@ -34030,7 +34026,7 @@
         <v>50</v>
       </c>
       <c r="I827" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="828">
@@ -34071,7 +34067,7 @@
         <v>45</v>
       </c>
       <c r="I828" t="n">
-        <v>3.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="829">
@@ -34112,7 +34108,7 @@
         <v>58</v>
       </c>
       <c r="I829" t="n">
-        <v>2.9</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="830">
@@ -34149,7 +34145,7 @@
         <v>22</v>
       </c>
       <c r="I830" t="n">
-        <v>6.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="831">
@@ -34190,7 +34186,7 @@
         <v>34</v>
       </c>
       <c r="I831" t="n">
-        <v>5.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="832">
@@ -34231,7 +34227,7 @@
         <v>28</v>
       </c>
       <c r="I832" t="n">
-        <v>5.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="833">
@@ -34272,7 +34268,7 @@
         <v>43</v>
       </c>
       <c r="I833" t="n">
-        <v>4.2</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="834">
@@ -34313,7 +34309,7 @@
         <v>52</v>
       </c>
       <c r="I834" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="835">
@@ -34354,7 +34350,7 @@
         <v>22</v>
       </c>
       <c r="I835" t="n">
-        <v>6.4</v>
+        <v>9.1</v>
       </c>
     </row>
     <row r="836">
@@ -34395,7 +34391,7 @@
         <v>45</v>
       </c>
       <c r="I836" t="n">
-        <v>3.9</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="837">
@@ -34475,7 +34471,7 @@
         <v>3</v>
       </c>
       <c r="I838" t="n">
-        <v>14.2</v>
+        <v>14.9</v>
       </c>
     </row>
     <row r="839">
@@ -34516,7 +34512,7 @@
         <v>66</v>
       </c>
       <c r="I839" t="n">
-        <v>1.9</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="840">
@@ -34549,7 +34545,7 @@
         <v>44</v>
       </c>
       <c r="I840" t="n">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="841">
@@ -34590,7 +34586,7 @@
         <v>61</v>
       </c>
       <c r="I841" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="842">
@@ -34631,7 +34627,7 @@
         <v>48</v>
       </c>
       <c r="I842" t="n">
-        <v>3.8</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="843">
@@ -34672,7 +34668,7 @@
         <v>15</v>
       </c>
       <c r="I843" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="844">
@@ -34791,7 +34787,7 @@
         <v>67</v>
       </c>
       <c r="I846" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="847">
@@ -34910,7 +34906,7 @@
         <v>71</v>
       </c>
       <c r="I849" t="n">
-        <v>0.9</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="850">
@@ -34947,7 +34943,7 @@
         <v>65</v>
       </c>
       <c r="I850" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="851">
@@ -34984,7 +34980,7 @@
         <v>67</v>
       </c>
       <c r="I851" t="n">
-        <v>1.6</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="852">
@@ -35025,7 +35021,7 @@
         <v>41</v>
       </c>
       <c r="I852" t="n">
-        <v>4.3</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="853">
@@ -35066,7 +35062,7 @@
         <v>70</v>
       </c>
       <c r="I853" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="854">
@@ -35107,7 +35103,7 @@
         <v>52</v>
       </c>
       <c r="I854" t="n">
-        <v>3.4</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="855">
@@ -35148,7 +35144,7 @@
         <v>5</v>
       </c>
       <c r="I855" t="n">
-        <v>10.5</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="856">
@@ -35189,7 +35185,7 @@
         <v>2</v>
       </c>
       <c r="I856" t="n">
-        <v>13.9</v>
+        <v>13.8</v>
       </c>
     </row>
     <row r="857">
@@ -35230,7 +35226,7 @@
         <v>15</v>
       </c>
       <c r="I857" t="n">
-        <v>6.5</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="858">
@@ -35271,7 +35267,7 @@
         <v>9</v>
       </c>
       <c r="I858" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="859">
@@ -35312,7 +35308,7 @@
         <v>16</v>
       </c>
       <c r="I859" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="860">
@@ -35353,7 +35349,7 @@
         <v>22</v>
       </c>
       <c r="I860" t="n">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="861">
@@ -35394,7 +35390,7 @@
         <v>1</v>
       </c>
       <c r="I861" t="n">
-        <v>16.5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="862">
@@ -35431,7 +35427,7 @@
         <v>23</v>
       </c>
       <c r="I862" t="n">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="863">
@@ -35472,7 +35468,7 @@
         <v>19</v>
       </c>
       <c r="I863" t="n">
-        <v>5.7</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="864">
@@ -35513,7 +35509,7 @@
         <v>19</v>
       </c>
       <c r="I864" t="n">
-        <v>5.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="865">
@@ -35554,7 +35550,7 @@
         <v>18</v>
       </c>
       <c r="I865" t="n">
-        <v>6</v>
+        <v>3.8</v>
       </c>
     </row>
     <row r="866">
@@ -35595,7 +35591,7 @@
         <v>3</v>
       </c>
       <c r="I866" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
     </row>
     <row r="867">
@@ -35636,7 +35632,7 @@
         <v>11</v>
       </c>
       <c r="I867" t="n">
-        <v>7.3</v>
+        <v>6.1</v>
       </c>
     </row>
     <row r="868">
@@ -35669,7 +35665,7 @@
         <v>17</v>
       </c>
       <c r="I868" t="n">
-        <v>6.3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="869">
@@ -35710,7 +35706,7 @@
         <v>30</v>
       </c>
       <c r="I869" t="n">
-        <v>3.4</v>
+        <v>4</v>
       </c>
     </row>
     <row r="870">
@@ -35751,7 +35747,7 @@
         <v>10</v>
       </c>
       <c r="I870" t="n">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="871">
@@ -35792,7 +35788,7 @@
         <v>4</v>
       </c>
       <c r="I871" t="n">
-        <v>10.8</v>
+        <v>13.4</v>
       </c>
     </row>
     <row r="872">
@@ -35833,7 +35829,7 @@
         <v>6</v>
       </c>
       <c r="I872" t="n">
-        <v>9.800000000000001</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="873">
@@ -35874,7 +35870,7 @@
         <v>27</v>
       </c>
       <c r="I873" t="n">
-        <v>3.8</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="874">
@@ -35915,7 +35911,7 @@
         <v>25</v>
       </c>
       <c r="I874" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="875">
@@ -35956,7 +35952,7 @@
         <v>36</v>
       </c>
       <c r="I875" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="876">
@@ -35993,7 +35989,7 @@
         <v>30</v>
       </c>
       <c r="I876" t="n">
-        <v>3.4</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="877">
@@ -36034,7 +36030,7 @@
         <v>13</v>
       </c>
       <c r="I877" t="n">
-        <v>7</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="878">
@@ -36114,7 +36110,7 @@
         <v>8</v>
       </c>
       <c r="I879" t="n">
-        <v>9.1</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="880">
@@ -36155,7 +36151,7 @@
         <v>28</v>
       </c>
       <c r="I880" t="n">
-        <v>3.7</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="881">
@@ -36196,7 +36192,7 @@
         <v>11</v>
       </c>
       <c r="I881" t="n">
-        <v>7.3</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="882">
@@ -36237,7 +36233,7 @@
         <v>33</v>
       </c>
       <c r="I882" t="n">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="883">
@@ -36358,7 +36354,7 @@
         <v>38</v>
       </c>
       <c r="I885" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="886">
@@ -36440,7 +36436,7 @@
         <v>21</v>
       </c>
       <c r="I887" t="n">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="888">
@@ -36481,7 +36477,7 @@
         <v>7</v>
       </c>
       <c r="I888" t="n">
-        <v>9.6</v>
+        <v>11.4</v>
       </c>
     </row>
     <row r="889">
@@ -36522,7 +36518,7 @@
         <v>34</v>
       </c>
       <c r="I889" t="n">
-        <v>2.5</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="890">
@@ -36602,7 +36598,7 @@
         <v>30</v>
       </c>
       <c r="I891" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="892">
@@ -36643,7 +36639,7 @@
         <v>24</v>
       </c>
       <c r="I892" t="n">
-        <v>4.6</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="893">
@@ -36684,7 +36680,7 @@
         <v>34</v>
       </c>
       <c r="I893" t="n">
-        <v>2.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="894">
@@ -36799,7 +36795,7 @@
         <v>25</v>
       </c>
       <c r="I896" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="897">
@@ -36881,7 +36877,7 @@
         <v>2</v>
       </c>
       <c r="I898" t="n">
-        <v>11.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="899">
@@ -36922,7 +36918,7 @@
         <v>5</v>
       </c>
       <c r="I899" t="n">
-        <v>7.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="900">
@@ -36963,7 +36959,7 @@
         <v>10</v>
       </c>
       <c r="I900" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="901">
@@ -37004,7 +37000,7 @@
         <v>35</v>
       </c>
       <c r="I901" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="902">
@@ -37045,7 +37041,7 @@
         <v>4</v>
       </c>
       <c r="I902" t="n">
-        <v>8.800000000000001</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="903">
@@ -37086,7 +37082,7 @@
         <v>9</v>
       </c>
       <c r="I903" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="904">
@@ -37127,7 +37123,7 @@
         <v>11</v>
       </c>
       <c r="I904" t="n">
-        <v>3.3</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="905">
@@ -37168,7 +37164,7 @@
         <v>1</v>
       </c>
       <c r="I905" t="n">
-        <v>12.7</v>
+        <v>13.1</v>
       </c>
     </row>
     <row r="906">
@@ -37209,7 +37205,7 @@
         <v>8</v>
       </c>
       <c r="I906" t="n">
-        <v>6.4</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="907">
@@ -37250,7 +37246,7 @@
         <v>6</v>
       </c>
       <c r="I907" t="n">
-        <v>6.8</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="908">
@@ -37287,7 +37283,7 @@
         <v>7</v>
       </c>
       <c r="I908" t="n">
-        <v>6.7</v>
+        <v>5.1</v>
       </c>
     </row>
     <row r="909">
@@ -37328,7 +37324,7 @@
         <v>19</v>
       </c>
       <c r="I909" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="910">
@@ -37369,7 +37365,7 @@
         <v>43</v>
       </c>
       <c r="I910" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="911">
@@ -37410,7 +37406,7 @@
         <v>35</v>
       </c>
       <c r="I911" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="912">
@@ -37451,7 +37447,7 @@
         <v>26</v>
       </c>
       <c r="I912" t="n">
-        <v>1.6</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="913">
@@ -37492,7 +37488,7 @@
         <v>23</v>
       </c>
       <c r="I913" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="914">
@@ -37533,7 +37529,7 @@
         <v>14</v>
       </c>
       <c r="I914" t="n">
-        <v>2.4</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="915">
@@ -37574,7 +37570,7 @@
         <v>29</v>
       </c>
       <c r="I915" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="916">
@@ -37615,7 +37611,7 @@
         <v>35</v>
       </c>
       <c r="I916" t="n">
-        <v>1.3</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="917">
@@ -37656,7 +37652,7 @@
         <v>35</v>
       </c>
       <c r="I917" t="n">
-        <v>1.3</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="918">
@@ -37736,7 +37732,7 @@
         <v>17</v>
       </c>
       <c r="I919" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="920">
@@ -37857,7 +37853,7 @@
         <v>3</v>
       </c>
       <c r="I922" t="n">
-        <v>11.4</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="923">
@@ -37898,7 +37894,7 @@
         <v>21</v>
       </c>
       <c r="I923" t="n">
-        <v>1.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="924">
@@ -37939,7 +37935,7 @@
         <v>26</v>
       </c>
       <c r="I924" t="n">
-        <v>1.6</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="925">
@@ -37980,7 +37976,7 @@
         <v>41</v>
       </c>
       <c r="I925" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="926">
@@ -38021,7 +38017,7 @@
         <v>29</v>
       </c>
       <c r="I926" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="927">
@@ -38062,7 +38058,7 @@
         <v>14</v>
       </c>
       <c r="I927" t="n">
-        <v>2.4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="928">
@@ -38103,7 +38099,7 @@
         <v>32</v>
       </c>
       <c r="I928" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="929">
@@ -38226,7 +38222,7 @@
         <v>20</v>
       </c>
       <c r="I931" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="932">
@@ -38263,7 +38259,7 @@
         <v>51</v>
       </c>
       <c r="I932" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="933">
@@ -38345,7 +38341,7 @@
         <v>13</v>
       </c>
       <c r="I934" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="935">
@@ -38386,7 +38382,7 @@
         <v>49</v>
       </c>
       <c r="I935" t="n">
-        <v>0.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="936">
@@ -38468,7 +38464,7 @@
         <v>23</v>
       </c>
       <c r="I937" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="938">
@@ -38509,7 +38505,7 @@
         <v>17</v>
       </c>
       <c r="I938" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="939">
@@ -38550,7 +38546,7 @@
         <v>29</v>
       </c>
       <c r="I939" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="940">
@@ -38591,7 +38587,7 @@
         <v>26</v>
       </c>
       <c r="I940" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="941">
@@ -38632,7 +38628,7 @@
         <v>32</v>
       </c>
       <c r="I941" t="n">
-        <v>1.4</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="942">
@@ -38673,7 +38669,7 @@
         <v>47</v>
       </c>
       <c r="I942" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="943">
@@ -38784,7 +38780,7 @@
         <v>12</v>
       </c>
       <c r="I945" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="946">
@@ -38864,7 +38860,7 @@
         <v>54</v>
       </c>
       <c r="I947" t="n">
-        <v>0.5</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="948">
@@ -38946,7 +38942,7 @@
         <v>32</v>
       </c>
       <c r="I949" t="n">
-        <v>1.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="950">
@@ -38987,7 +38983,7 @@
         <v>43</v>
       </c>
       <c r="I950" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="951">
@@ -39067,7 +39063,7 @@
         <v>35</v>
       </c>
       <c r="I952" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="953">
@@ -39100,7 +39096,7 @@
         <v>54</v>
       </c>
       <c r="I953" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="954">
@@ -39141,7 +39137,7 @@
         <v>54</v>
       </c>
       <c r="I954" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="955">
@@ -39182,7 +39178,7 @@
         <v>41</v>
       </c>
       <c r="I955" t="n">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="956">
@@ -39219,7 +39215,7 @@
         <v>21</v>
       </c>
       <c r="I956" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="957">
@@ -39260,7 +39256,7 @@
         <v>35</v>
       </c>
       <c r="I957" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="958">
@@ -39301,7 +39297,7 @@
         <v>58</v>
       </c>
       <c r="I958" t="n">
-        <v>0.4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="959">
@@ -39342,7 +39338,7 @@
         <v>58</v>
       </c>
       <c r="I959" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="960">
@@ -39383,7 +39379,7 @@
         <v>43</v>
       </c>
       <c r="I960" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="961">
@@ -39424,7 +39420,7 @@
         <v>54</v>
       </c>
       <c r="I961" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="962">
@@ -39465,7 +39461,7 @@
         <v>15</v>
       </c>
       <c r="I962" t="n">
-        <v>6.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="963">
@@ -39506,7 +39502,7 @@
         <v>2</v>
       </c>
       <c r="I963" t="n">
-        <v>10.4</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="964">
@@ -39547,7 +39543,7 @@
         <v>26</v>
       </c>
       <c r="I964" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="965">
@@ -39588,7 +39584,7 @@
         <v>27</v>
       </c>
       <c r="I965" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="966">
@@ -39629,7 +39625,7 @@
         <v>25</v>
       </c>
       <c r="I966" t="n">
-        <v>5.1</v>
+        <v>5.9</v>
       </c>
     </row>
     <row r="967">
@@ -39670,7 +39666,7 @@
         <v>10</v>
       </c>
       <c r="I967" t="n">
-        <v>7.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="968">
@@ -39711,7 +39707,7 @@
         <v>10</v>
       </c>
       <c r="I968" t="n">
-        <v>7.5</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="969">
@@ -39752,7 +39748,7 @@
         <v>29</v>
       </c>
       <c r="I969" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="970">
@@ -39793,7 +39789,7 @@
         <v>13</v>
       </c>
       <c r="I970" t="n">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="971">
@@ -39834,7 +39830,7 @@
         <v>50</v>
       </c>
       <c r="I971" t="n">
-        <v>2.4</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="972">
@@ -39875,7 +39871,7 @@
         <v>16</v>
       </c>
       <c r="I972" t="n">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="973">
@@ -39916,7 +39912,7 @@
         <v>8</v>
       </c>
       <c r="I973" t="n">
-        <v>7.8</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="974">
@@ -39957,7 +39953,7 @@
         <v>36</v>
       </c>
       <c r="I974" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="975">
@@ -39998,7 +39994,7 @@
         <v>28</v>
       </c>
       <c r="I975" t="n">
-        <v>4.7</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="976">
@@ -40039,7 +40035,7 @@
         <v>3</v>
       </c>
       <c r="I976" t="n">
-        <v>10.2</v>
+        <v>8.9</v>
       </c>
     </row>
     <row r="977">
@@ -40121,7 +40117,7 @@
         <v>4</v>
       </c>
       <c r="I978" t="n">
-        <v>10.1</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="979">
@@ -40162,7 +40158,7 @@
         <v>47</v>
       </c>
       <c r="I979" t="n">
-        <v>2.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="980">
@@ -40203,7 +40199,7 @@
         <v>46</v>
       </c>
       <c r="I980" t="n">
-        <v>2.8</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="981">
@@ -40244,7 +40240,7 @@
         <v>5</v>
       </c>
       <c r="I981" t="n">
-        <v>9.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="982">
@@ -40285,7 +40281,7 @@
         <v>58</v>
       </c>
       <c r="I982" t="n">
-        <v>1.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="983">
@@ -40361,7 +40357,7 @@
         <v>18</v>
       </c>
       <c r="I984" t="n">
-        <v>5.8</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="985">
@@ -40402,7 +40398,7 @@
         <v>51</v>
       </c>
       <c r="I985" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="986">
@@ -40443,7 +40439,7 @@
         <v>17</v>
       </c>
       <c r="I986" t="n">
-        <v>5.9</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="987">
@@ -40484,7 +40480,7 @@
         <v>9</v>
       </c>
       <c r="I987" t="n">
-        <v>7.6</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="988">
@@ -40525,7 +40521,7 @@
         <v>57</v>
       </c>
       <c r="I988" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="989">
@@ -40566,7 +40562,7 @@
         <v>20</v>
       </c>
       <c r="I989" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="990">
@@ -40607,7 +40603,7 @@
         <v>37</v>
       </c>
       <c r="I990" t="n">
-        <v>4.1</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="991">
@@ -40648,7 +40644,7 @@
         <v>33</v>
       </c>
       <c r="I991" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="992">
@@ -40689,7 +40685,7 @@
         <v>47</v>
       </c>
       <c r="I992" t="n">
-        <v>2.5</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="993">
@@ -40730,7 +40726,7 @@
         <v>20</v>
       </c>
       <c r="I993" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="994">
@@ -40771,7 +40767,7 @@
         <v>42</v>
       </c>
       <c r="I994" t="n">
-        <v>3.2</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="995">
@@ -40812,7 +40808,7 @@
         <v>24</v>
       </c>
       <c r="I995" t="n">
-        <v>5.2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="996">
@@ -40853,7 +40849,7 @@
         <v>41</v>
       </c>
       <c r="I996" t="n">
-        <v>3.3</v>
+        <v>4.8</v>
       </c>
     </row>
     <row r="997">
@@ -40894,7 +40890,7 @@
         <v>33</v>
       </c>
       <c r="I997" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="998">
@@ -40935,7 +40931,7 @@
         <v>51</v>
       </c>
       <c r="I998" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="999">
@@ -40976,7 +40972,7 @@
         <v>44</v>
       </c>
       <c r="I999" t="n">
-        <v>3</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="1000">
@@ -41017,7 +41013,7 @@
         <v>23</v>
       </c>
       <c r="I1000" t="n">
-        <v>5.3</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="1001">
@@ -41058,7 +41054,7 @@
         <v>40</v>
       </c>
       <c r="I1001" t="n">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="1002">
@@ -41099,7 +41095,7 @@
         <v>1</v>
       </c>
       <c r="I1002" t="n">
-        <v>13.1</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="1003">
@@ -41140,7 +41136,7 @@
         <v>7</v>
       </c>
       <c r="I1003" t="n">
-        <v>7.9</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="1004">
@@ -41181,7 +41177,7 @@
         <v>32</v>
       </c>
       <c r="I1004" t="n">
-        <v>4.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="1005">
@@ -41222,7 +41218,7 @@
         <v>31</v>
       </c>
       <c r="I1005" t="n">
-        <v>4.5</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="1006">
@@ -41263,7 +41259,7 @@
         <v>43</v>
       </c>
       <c r="I1006" t="n">
-        <v>3.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="1007">
@@ -41304,7 +41300,7 @@
         <v>12</v>
       </c>
       <c r="I1007" t="n">
-        <v>7.4</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="1008">
@@ -41380,7 +41376,7 @@
         <v>39</v>
       </c>
       <c r="I1009" t="n">
-        <v>3.8</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="1010">
@@ -41421,7 +41417,7 @@
         <v>55</v>
       </c>
       <c r="I1010" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="1011">
@@ -41462,7 +41458,7 @@
         <v>14</v>
       </c>
       <c r="I1011" t="n">
-        <v>6.9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1012">
@@ -41503,7 +41499,7 @@
         <v>54</v>
       </c>
       <c r="I1012" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1013">
@@ -41544,7 +41540,7 @@
         <v>44</v>
       </c>
       <c r="I1013" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="1014">
@@ -41581,7 +41577,7 @@
         <v>53</v>
       </c>
       <c r="I1014" t="n">
-        <v>2.1</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="1015">
@@ -41622,7 +41618,7 @@
         <v>55</v>
       </c>
       <c r="I1015" t="n">
-        <v>1.6</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="1016">
@@ -41702,7 +41698,7 @@
         <v>33</v>
       </c>
       <c r="I1017" t="n">
-        <v>4.3</v>
+        <v>5.2</v>
       </c>
     </row>
     <row r="1018">
@@ -41782,7 +41778,7 @@
         <v>29</v>
       </c>
       <c r="I1019" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="1020">
@@ -41823,7 +41819,7 @@
         <v>19</v>
       </c>
       <c r="I1020" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="1021">
@@ -41903,7 +41899,7 @@
         <v>22</v>
       </c>
       <c r="I1022" t="n">
-        <v>5.4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1023">
@@ -41944,7 +41940,7 @@
         <v>47</v>
       </c>
       <c r="I1023" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1024">
@@ -42020,7 +42016,7 @@
         <v>37</v>
       </c>
       <c r="I1025" t="n">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="1026">
@@ -42061,7 +42057,7 @@
         <v>30</v>
       </c>
       <c r="I1026" t="n">
-        <v>2.1</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1027">
@@ -42102,7 +42098,7 @@
         <v>23</v>
       </c>
       <c r="I1027" t="n">
-        <v>2.5</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="1028">
@@ -42143,7 +42139,7 @@
         <v>35</v>
       </c>
       <c r="I1028" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="1029">
@@ -42184,7 +42180,7 @@
         <v>20</v>
       </c>
       <c r="I1029" t="n">
-        <v>2.6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1030">
@@ -42225,7 +42221,7 @@
         <v>35</v>
       </c>
       <c r="I1030" t="n">
-        <v>1.9</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1031">
@@ -42266,7 +42262,7 @@
         <v>8</v>
       </c>
       <c r="I1031" t="n">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="1032">
@@ -42307,7 +42303,7 @@
         <v>7</v>
       </c>
       <c r="I1032" t="n">
-        <v>6.5</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="1033">
@@ -42348,7 +42344,7 @@
         <v>11</v>
       </c>
       <c r="I1033" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="1034">
@@ -42389,7 +42385,7 @@
         <v>47</v>
       </c>
       <c r="I1034" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="1035">
@@ -42430,7 +42426,7 @@
         <v>23</v>
       </c>
       <c r="I1035" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1036">
@@ -42471,7 +42467,7 @@
         <v>23</v>
       </c>
       <c r="I1036" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="1037">
@@ -42512,7 +42508,7 @@
         <v>2</v>
       </c>
       <c r="I1037" t="n">
-        <v>10.5</v>
+        <v>11.3</v>
       </c>
     </row>
     <row r="1038">
@@ -42553,7 +42549,7 @@
         <v>1</v>
       </c>
       <c r="I1038" t="n">
-        <v>12</v>
+        <v>15.9</v>
       </c>
     </row>
     <row r="1039">
@@ -42594,7 +42590,7 @@
         <v>3</v>
       </c>
       <c r="I1039" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="1040">
@@ -42635,7 +42631,7 @@
         <v>39</v>
       </c>
       <c r="I1040" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="1041">
@@ -42715,7 +42711,7 @@
         <v>6</v>
       </c>
       <c r="I1042" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="1043">
@@ -42756,7 +42752,7 @@
         <v>39</v>
       </c>
       <c r="I1043" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="1044">
@@ -42793,7 +42789,7 @@
         <v>44</v>
       </c>
       <c r="I1044" t="n">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="1045">
@@ -42834,7 +42830,7 @@
         <v>50</v>
       </c>
       <c r="I1045" t="n">
-        <v>1.4</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="1046">
@@ -42875,7 +42871,7 @@
         <v>12</v>
       </c>
       <c r="I1046" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1047">
@@ -42916,7 +42912,7 @@
         <v>47</v>
       </c>
       <c r="I1047" t="n">
-        <v>1.5</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="1048">
@@ -42957,7 +42953,7 @@
         <v>39</v>
       </c>
       <c r="I1048" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="1049">
@@ -42998,7 +42994,7 @@
         <v>18</v>
       </c>
       <c r="I1049" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1050">
@@ -43039,7 +43035,7 @@
         <v>35</v>
       </c>
       <c r="I1050" t="n">
-        <v>1.9</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1051">
@@ -43080,7 +43076,7 @@
         <v>30</v>
       </c>
       <c r="I1051" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="1052">
@@ -43121,7 +43117,7 @@
         <v>5</v>
       </c>
       <c r="I1052" t="n">
-        <v>7.2</v>
+        <v>6.9</v>
       </c>
     </row>
     <row r="1053">
@@ -43203,7 +43199,7 @@
         <v>35</v>
       </c>
       <c r="I1054" t="n">
-        <v>1.9</v>
+        <v>2.3</v>
       </c>
     </row>
     <row r="1055">
@@ -43244,7 +43240,7 @@
         <v>45</v>
       </c>
       <c r="I1055" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="1056">
@@ -43285,7 +43281,7 @@
         <v>28</v>
       </c>
       <c r="I1056" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1057">
@@ -43365,7 +43361,7 @@
         <v>54</v>
       </c>
       <c r="I1058" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1059">
@@ -43406,7 +43402,7 @@
         <v>33</v>
       </c>
       <c r="I1059" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1060">
@@ -43443,7 +43439,7 @@
         <v>54</v>
       </c>
       <c r="I1060" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1061">
@@ -43484,7 +43480,7 @@
         <v>13</v>
       </c>
       <c r="I1061" t="n">
-        <v>3.4</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="1062">
@@ -43525,7 +43521,7 @@
         <v>14</v>
       </c>
       <c r="I1062" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1063">
@@ -43566,7 +43562,7 @@
         <v>4</v>
       </c>
       <c r="I1063" t="n">
-        <v>7.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="1064">
@@ -43607,7 +43603,7 @@
         <v>10</v>
       </c>
       <c r="I1064" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="1065">
@@ -43648,7 +43644,7 @@
         <v>15</v>
       </c>
       <c r="I1065" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1066">
@@ -43685,7 +43681,7 @@
         <v>20</v>
       </c>
       <c r="I1066" t="n">
-        <v>2.6</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1067">
@@ -43726,7 +43722,7 @@
         <v>15</v>
       </c>
       <c r="I1067" t="n">
-        <v>2.9</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1068">
@@ -43767,7 +43763,7 @@
         <v>18</v>
       </c>
       <c r="I1068" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1069">
@@ -43808,7 +43804,7 @@
         <v>47</v>
       </c>
       <c r="I1069" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="1070">
@@ -43849,7 +43845,7 @@
         <v>8</v>
       </c>
       <c r="I1070" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="1071">
@@ -43890,7 +43886,7 @@
         <v>30</v>
       </c>
       <c r="I1071" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1072">
@@ -43931,7 +43927,7 @@
         <v>17</v>
       </c>
       <c r="I1072" t="n">
-        <v>2.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="1073">
@@ -43972,7 +43968,7 @@
         <v>33</v>
       </c>
       <c r="I1073" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="1074">
@@ -44132,7 +44128,7 @@
         <v>23</v>
       </c>
       <c r="I1077" t="n">
-        <v>2.5</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="1078">
@@ -44173,7 +44169,7 @@
         <v>39</v>
       </c>
       <c r="I1078" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="1079">
@@ -44214,7 +44210,7 @@
         <v>28</v>
       </c>
       <c r="I1079" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="1080">
@@ -44255,7 +44251,7 @@
         <v>51</v>
       </c>
       <c r="I1080" t="n">
-        <v>1.3</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="1081">
@@ -44296,7 +44292,7 @@
         <v>45</v>
       </c>
       <c r="I1081" t="n">
-        <v>1.6</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="1082">
@@ -44417,7 +44413,7 @@
         <v>27</v>
       </c>
       <c r="I1084" t="n">
-        <v>2.4</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="1085">
@@ -44538,7 +44534,7 @@
         <v>1</v>
       </c>
       <c r="I1087" t="n">
-        <v>10.4</v>
+        <v>10.1</v>
       </c>
     </row>
     <row r="1088">
@@ -44579,7 +44575,7 @@
         <v>20</v>
       </c>
       <c r="I1088" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
     </row>
     <row r="1089">
@@ -44620,7 +44616,7 @@
         <v>15</v>
       </c>
       <c r="I1089" t="n">
-        <v>5.1</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="1090">
@@ -44661,7 +44657,7 @@
         <v>6</v>
       </c>
       <c r="I1090" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="1091">
@@ -44702,7 +44698,7 @@
         <v>8</v>
       </c>
       <c r="I1091" t="n">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="1092">
@@ -44743,7 +44739,7 @@
         <v>2</v>
       </c>
       <c r="I1092" t="n">
-        <v>10</v>
+        <v>10.6</v>
       </c>
     </row>
     <row r="1093">
@@ -44784,7 +44780,7 @@
         <v>8</v>
       </c>
       <c r="I1093" t="n">
-        <v>7.3</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="1094">
@@ -44825,7 +44821,7 @@
         <v>6</v>
       </c>
       <c r="I1094" t="n">
-        <v>7.4</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="1095">
@@ -44866,7 +44862,7 @@
         <v>4</v>
       </c>
       <c r="I1095" t="n">
-        <v>8.699999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="1096">
@@ -44907,7 +44903,7 @@
         <v>3</v>
       </c>
       <c r="I1096" t="n">
-        <v>9.9</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="1097">
@@ -44948,7 +44944,7 @@
         <v>14</v>
       </c>
       <c r="I1097" t="n">
-        <v>5.4</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="1098">
@@ -44989,7 +44985,7 @@
         <v>27</v>
       </c>
       <c r="I1098" t="n">
-        <v>1.3</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="1099">
@@ -45069,7 +45065,7 @@
         <v>11</v>
       </c>
       <c r="I1100" t="n">
-        <v>6.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="1101">
@@ -45110,7 +45106,7 @@
         <v>16</v>
       </c>
       <c r="I1101" t="n">
-        <v>4.9</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="1102">
@@ -45151,7 +45147,7 @@
         <v>13</v>
       </c>
       <c r="I1102" t="n">
-        <v>6</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="1103">
@@ -45231,7 +45227,7 @@
         <v>18</v>
       </c>
       <c r="I1104" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="1105">
@@ -45272,7 +45268,7 @@
         <v>10</v>
       </c>
       <c r="I1105" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="1106">
@@ -45313,7 +45309,7 @@
         <v>17</v>
       </c>
       <c r="I1106" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="1107">
@@ -45354,7 +45350,7 @@
         <v>12</v>
       </c>
       <c r="I1107" t="n">
-        <v>6.3</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="1108">
@@ -45395,7 +45391,7 @@
         <v>22</v>
       </c>
       <c r="I1108" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1109">
@@ -45436,7 +45432,7 @@
         <v>23</v>
       </c>
       <c r="I1109" t="n">
-        <v>3.4</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="1110">
@@ -45664,7 +45660,7 @@
         <v>25</v>
       </c>
       <c r="I1115" t="n">
-        <v>2.1</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1116">
@@ -45705,7 +45701,7 @@
         <v>24</v>
       </c>
       <c r="I1116" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="1117">
@@ -45820,7 +45816,7 @@
         <v>10</v>
       </c>
       <c r="I1119" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="1120">
@@ -45861,7 +45857,7 @@
         <v>14</v>
       </c>
       <c r="I1120" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="1121">
@@ -45902,7 +45898,7 @@
         <v>9</v>
       </c>
       <c r="I1121" t="n">
-        <v>6.3</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="1122">
@@ -45943,7 +45939,7 @@
         <v>1</v>
       </c>
       <c r="I1122" t="n">
-        <v>14.2</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="1123">
@@ -45984,7 +45980,7 @@
         <v>31</v>
       </c>
       <c r="I1123" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="1124">
@@ -46025,7 +46021,7 @@
         <v>4</v>
       </c>
       <c r="I1124" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="1125">
@@ -46066,7 +46062,7 @@
         <v>37</v>
       </c>
       <c r="I1125" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1126">
@@ -46107,7 +46103,7 @@
         <v>19</v>
       </c>
       <c r="I1126" t="n">
-        <v>4</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="1127">
@@ -46148,7 +46144,7 @@
         <v>26</v>
       </c>
       <c r="I1127" t="n">
-        <v>3.1</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="1128">
@@ -46189,7 +46185,7 @@
         <v>30</v>
       </c>
       <c r="I1128" t="n">
-        <v>2.5</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1129">
@@ -46230,7 +46226,7 @@
         <v>22</v>
       </c>
       <c r="I1129" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1130">
@@ -46271,7 +46267,7 @@
         <v>14</v>
       </c>
       <c r="I1130" t="n">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="1131">
@@ -46351,7 +46347,7 @@
         <v>20</v>
       </c>
       <c r="I1132" t="n">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
     </row>
     <row r="1133">
@@ -46392,7 +46388,7 @@
         <v>13</v>
       </c>
       <c r="I1133" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="1134">
@@ -46433,7 +46429,7 @@
         <v>24</v>
       </c>
       <c r="I1134" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1135">
@@ -46474,7 +46470,7 @@
         <v>36</v>
       </c>
       <c r="I1135" t="n">
-        <v>1.6</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="1136">
@@ -46556,7 +46552,7 @@
         <v>8</v>
       </c>
       <c r="I1137" t="n">
-        <v>6.6</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="1138">
@@ -46597,7 +46593,7 @@
         <v>16</v>
       </c>
       <c r="I1138" t="n">
-        <v>5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="1139">
@@ -46638,7 +46634,7 @@
         <v>6</v>
       </c>
       <c r="I1139" t="n">
-        <v>8.4</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="1140">
@@ -46679,7 +46675,7 @@
         <v>37</v>
       </c>
       <c r="I1140" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="1141">
@@ -46720,7 +46716,7 @@
         <v>24</v>
       </c>
       <c r="I1141" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1142">
@@ -46761,7 +46757,7 @@
         <v>31</v>
       </c>
       <c r="I1142" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="1143">
@@ -46798,7 +46794,7 @@
         <v>39</v>
       </c>
       <c r="I1143" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="1144">
@@ -46839,7 +46835,7 @@
         <v>20</v>
       </c>
       <c r="I1144" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
     </row>
     <row r="1145">
@@ -46880,7 +46876,7 @@
         <v>33</v>
       </c>
       <c r="I1145" t="n">
-        <v>2.2</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="1146">
@@ -46921,7 +46917,7 @@
         <v>6</v>
       </c>
       <c r="I1146" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="1147">
@@ -47003,7 +46999,7 @@
         <v>10</v>
       </c>
       <c r="I1148" t="n">
-        <v>5.9</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="1149">
@@ -47044,7 +47040,7 @@
         <v>18</v>
       </c>
       <c r="I1149" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="1150">
@@ -47085,7 +47081,7 @@
         <v>12</v>
       </c>
       <c r="I1150" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="1151">
@@ -47126,7 +47122,7 @@
         <v>35</v>
       </c>
       <c r="I1151" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="1152">
@@ -47167,7 +47163,7 @@
         <v>34</v>
       </c>
       <c r="I1152" t="n">
-        <v>2.1</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="1153">
@@ -47208,7 +47204,7 @@
         <v>2</v>
       </c>
       <c r="I1153" t="n">
-        <v>11.2</v>
+        <v>12.2</v>
       </c>
     </row>
     <row r="1154">
@@ -47249,7 +47245,7 @@
         <v>29</v>
       </c>
       <c r="I1154" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="1155">
@@ -47290,7 +47286,7 @@
         <v>26</v>
       </c>
       <c r="I1155" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="1156">
@@ -47331,7 +47327,7 @@
         <v>23</v>
       </c>
       <c r="I1156" t="n">
-        <v>3.3</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="1157">
@@ -47372,7 +47368,7 @@
         <v>3</v>
       </c>
       <c r="I1157" t="n">
-        <v>10</v>
+        <v>10.7</v>
       </c>
     </row>
     <row r="1158">
@@ -47405,7 +47401,7 @@
         <v>17</v>
       </c>
       <c r="I1158" t="n">
-        <v>4.9</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="1159">
@@ -47446,7 +47442,7 @@
         <v>4</v>
       </c>
       <c r="I1159" t="n">
-        <v>6.8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1160">
@@ -47487,7 +47483,7 @@
         <v>5</v>
       </c>
       <c r="I1160" t="n">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
     </row>
     <row r="1161">
@@ -47528,7 +47524,7 @@
         <v>7</v>
       </c>
       <c r="I1161" t="n">
-        <v>5.2</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="1162">
@@ -47569,7 +47565,7 @@
         <v>13</v>
       </c>
       <c r="I1162" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1163">
@@ -47610,7 +47606,7 @@
         <v>10</v>
       </c>
       <c r="I1163" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="1164">
@@ -47651,7 +47647,7 @@
         <v>5</v>
       </c>
       <c r="I1164" t="n">
-        <v>5.4</v>
+        <v>4.6</v>
       </c>
     </row>
     <row r="1165">
@@ -47692,7 +47688,7 @@
         <v>1</v>
       </c>
       <c r="I1165" t="n">
-        <v>9.699999999999999</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1166">
@@ -47733,7 +47729,7 @@
         <v>13</v>
       </c>
       <c r="I1166" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
     </row>
     <row r="1167">
@@ -47774,7 +47770,7 @@
         <v>13</v>
       </c>
       <c r="I1167" t="n">
-        <v>3</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="1168">
@@ -47815,7 +47811,7 @@
         <v>12</v>
       </c>
       <c r="I1168" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1169">
@@ -47856,7 +47852,7 @@
         <v>3</v>
       </c>
       <c r="I1169" t="n">
-        <v>7.3</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="1170">
@@ -47897,7 +47893,7 @@
         <v>2</v>
       </c>
       <c r="I1170" t="n">
-        <v>7.6</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="1171">
@@ -47938,7 +47934,7 @@
         <v>8</v>
       </c>
       <c r="I1171" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
     </row>
     <row r="1172">
@@ -47979,7 +47975,7 @@
         <v>9</v>
       </c>
       <c r="I1172" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
     </row>
     <row r="1173">
@@ -48020,7 +48016,7 @@
         <v>21</v>
       </c>
       <c r="I1173" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1174">
@@ -48061,7 +48057,7 @@
         <v>10</v>
       </c>
       <c r="I1174" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="1175">
@@ -48102,7 +48098,7 @@
         <v>19</v>
       </c>
       <c r="I1175" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="1176">
@@ -48143,7 +48139,7 @@
         <v>25</v>
       </c>
       <c r="I1176" t="n">
-        <v>1.2</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="1177">
@@ -48184,7 +48180,7 @@
         <v>16</v>
       </c>
       <c r="I1177" t="n">
-        <v>2.7</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="1178">
@@ -48225,7 +48221,7 @@
         <v>22</v>
       </c>
       <c r="I1178" t="n">
-        <v>2.2</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1179">
@@ -48266,7 +48262,7 @@
         <v>19</v>
       </c>
       <c r="I1179" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="1180">
@@ -48307,7 +48303,7 @@
         <v>26</v>
       </c>
       <c r="I1180" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1181">
@@ -48348,7 +48344,7 @@
         <v>18</v>
       </c>
       <c r="I1181" t="n">
-        <v>2.5</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="1182">
@@ -48389,7 +48385,7 @@
         <v>24</v>
       </c>
       <c r="I1182" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
     </row>
     <row r="1183">
@@ -48430,7 +48426,7 @@
         <v>22</v>
       </c>
       <c r="I1183" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="1184">
@@ -48471,7 +48467,7 @@
         <v>16</v>
       </c>
       <c r="I1184" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="1185">
